--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD38DAD6-9453-4444-B883-903D8D3FA4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC77A07-07E1-410E-A6BA-7FFFE1916937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{3F73E7A1-BED8-47DA-9622-B74B1E14BF28}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2928" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="1747">
   <si>
     <t>message</t>
   </si>
@@ -3985,6 +3985,1296 @@
   </si>
   <si>
     <t>592437224486</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 75.00 UPI/SBIN/513790184764/MIHAL  PALAKK Bal:Rs 20349.88 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>MIHAL  PALAKK</t>
+  </si>
+  <si>
+    <t>South Indian Bank</t>
+  </si>
+  <si>
+    <t>DEBIT</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 100.00 UPI/KLGB/512805384242/NIDHA  RAHMA/ Bal:Rs 20942.48 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 40.00 UPI/SBIN/513568443202/MIHAL  PALAKK Bal:Rs 20425.78 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 63.00 UPI/JIOP/512822945838/JIO MART/UPI Bal:Rs 20879.48 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 540.90 UPI/ICIC/513568982781/Google India  Bal:Rs 19884.88 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 27.00 UPI/SBIN/549323958969/Shadin Hafizu Bal:Rs 21042.48 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 50.00 UPI/JIOP/549351364210/JIO MART/UPI Bal:Rs 21069.48 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 230.00 UPI/YESB/511546376094/SAINUDHEEN  A Bal:Rs 20064.48 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 40.00 UPI/YESB/511165775193/C1 CUSAT REST Bal:Rs 20680.36 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 72.64 UPI/SBIN/511043232351/MIHAL  PALAKK Bal:Rs 19861.26 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 23.00 UPI/UTIB/510778891856/Google India  Bal:Rs 19985.15 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 90.00 UPI/YESB/510669306846/IRCTC UTS/UPI Bal:Rs 19690.15 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 65.00 UPI/SBIN/510287696316/Indian Railwa Bal:Rs 19790.15 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 96.00 UPI/UTIB/509925087542/Swiggy Limite Bal:Rs 21825.75 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 75.00 UPI/UTIB/509612622844/Swiggy Limite Bal:Rs 22152.65 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 150.00 UPI/YESB/508763205837/IRCTC UTS/UPI Bal:Rs 20145.65 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 30.00 UPI/FDRL/544792370370/MOHAMED SAFEE Bal:Rs 16685.65 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 75.00 UPI/SBIN/507855022919/MIHAL  PALAKK Bal:Rs 13980.92 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 60.00 UPI/DLXB/507448369107/GAYATHRI/UPI Bal:Rs 14427.92 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 100.00 UPI/YESB/507410313412/Ishak V T/UPI Bal:Rs 14487.92 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 25.00 UPI/FDRL/507289848857/MOHAMED SAFEE Bal:Rs 14587.92 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 2997.00 UPI/SBIN/507238033790/AKASH  K/ruva Bal:Rs 14702.92 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 3250.00 UPI/SBIN/506539123537/Mr HAIMEN  DC Bal:Rs 15423.89 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 40.00 UPI/YESB/504391676575/SHEFEEQ P U/U Bal:Rs 15450.79 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 74.99 UPI/SBIN/504381457636/MIHAL  PALAKK Bal:Rs 15490.79 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 20.00 UPI/ICIC/540723124345/AKSHAY GOPAKU Bal:Rs 15595.78 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 3376.00 UPI/SBIN/503773856454/Mr HAIMEN  DC Bal:Rs 16094.78 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 65.00 UPI/SBIN/502314653274/MIHAL  PALAKK Bal:Rs 13265.78 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 10.00 UPI/YESB/501841012637/BIBIN MILLENT Bal:Rs 13617.19 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 3.00 UPI/UTIB/501637054557/Mavinchoode 3 Bal:Rs 13682.19 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 370.90 UPI/ICIC/501486312493/Google India  Bal:Rs 13715.19 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 20.00 UPI/ICIC/501306053528/AKSHAY GOPAKU Bal:Rs 14116.09 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 100.00 UPI/SBIN/501210844126/MIHAL  PALAKK Bal:Rs 14136.09 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 20.00 UPI/YESB/500750608612/SHEFEEQ P U/U Bal:Rs 13583.59 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 33.00 UPI/ICIC/436522933901/Google India  Bal:Rs 13970.85 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 20.00 UPI/SBIN/434519395558/MIHAL  PALAKK Bal:Rs 14920.95 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 1890.00 UPI/FDRL/434140238243/AKASH K/UPI Bal:Rs 14973.61 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 1000.00 UPI/FDRL/434140272870/AKASH K/UPI Bal:Rs 16863.61 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 3345.00 UPI/SBIN/434001106525/Mr HAIMEN  DC Bal:Rs 17823.94 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 65.00 UPI/YESB/433732421779/IRCTC UTS/UPI Bal:Rs 14671.94 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 32.00 UPI/SBIN/433333360119/ROSE  MARIA/U Bal:Rs 14721.94 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 130.00 UPI/YESB/433329232099/C1 CUSAT REST Bal:Rs 14798.94 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 29.75 UPI/SBIN/433306887568/Firoz  Zaman/ Bal:Rs 14926.28 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 147.00 UPI/YESB/433232586093/ABDUL  SALAM  Bal:Rs 14919.28 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 70.00 UPI/YESB/432824358080/KALPAKA TRANS Bal:Rs 15313.86 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 480.90 UPI/UTIB/432592331178/Google India  Bal:Rs 14657.86 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 64.29 UPI/SBIN/469093966926/NEMA  FATHIMA Bal:Rs 15156.76 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 40.00 UPI/ICIC/432336233460/AKSHAY GOPAKU Bal:Rs 15221.05 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 120.00 UPI/HDFC/432063641912/RISHI KRISHNA Bal:Rs 15291.05 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 8.00 UPI/ICIC/468623332583/AKSHAY GOPAKU Bal:Rs 15445.05 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 40.00 UPI/YESB/431999120100/ASHA  MARIYA/ Bal:Rs 15473.05 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 20.00 UPI/HDFC/431798587461/RISHI KRISHNA Bal:Rs 15543.05 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 10.00 UPI/CNRB/431629062707/VISHNU P RAJA Bal:Rs 15563.05 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 10.00 UPI/YESB/431516489847/C1 CUSAT REST Bal:Rs 18587.05 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 83.75 UPI/SBIN/431468291533/MIHAL  PALAKK Bal:Rs 15213.05 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 10.00 UPI/SBIN/431391974662/Leonard  Varg Bal:Rs 15419.80 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 15.00 UPI/ICIC/431224708899/AKSHAY GOPAKU Bal:Rs 15474.80 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 350.00 UPI/CNRB/431233157396/SANA  NOUSHAD Bal:Rs 15489.80 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 15.00 UPI/SBIN/431052196448/ROSE  MARIA/U Bal:Rs 19199.80 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs 1500.00 UPI/SBIN/428567290288/AKASH  K/UPI Bal:Rs 17368.99 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.9.00 UPI/YESB/427694580608/C2 CUSATRESTA Bal:Rs.15446.49 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/SBIN/427533579238/MIHAL  PALAKK Bal:Rs.15455.49 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/ICIC/463503700812/AKSHAY GOPAKU Bal:Rs.14207.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/ICIC/426785884938/AKSHAY GOPAKU Bal:Rs.14262.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.45.00 UPI/SBIN/426733434338/MIHAL  PALAKK Bal:Rs.14282.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.70.00 UPI/YESB/426695098291/IRCTC UTS/UPI Bal:Rs.12827.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.22.00 UPI/UTIB/426061519046/Google India  Bal:Rs.12952.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.22.00 UPI/UTIB/425912718767/Google India  Bal:Rs.12974.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.65.00 UPI/YESB/425709850517/IRCTC UTS/UPI Bal:Rs.13032.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.312.00 UPI/YESB/425645589558/JALEEL K H/UP Bal:Rs.12925.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.40.00 UPI/SBIN/425660199644/MIHAL  PALAKK Bal:Rs.13237.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/YESB/462160969985/SHEFEEQ P U/U Bal:Rs.13277.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/YESB/425463325072/ABDUL SALAM K Bal:Rs.15225.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.800.00 UPI/FDRL/425289584586/NIDAL C M P/o Bal:Rs.14255.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.179.00 UPI/YESB/425146062318/AVANEESH P A/ Bal:Rs.9781.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.60.00 UPI/YESB/425110967737/C2 CUSATRESTA Bal:Rs.9942.39 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.70.00 UPI/YESB/460740357681/IRCTC UTS/UPI Bal:Rs.11951.37 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.231.00 UPI/FDRL/424026050979/MP MART LLP B Bal:Rs.12021.37 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.500.00 UPI/SBIN/423907144048/ROMAL  JOSBIN Bal:Rs.12252.37 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.60.00 UPI/SIBL/460348226551/ARSHAD/UPI Bal:Rs.12967.37 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.70.00 UPI/FDRL/423697179107/ABSE ABDUL VA Bal:Rs.13022.37 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.140.00 UPI/YESB/423695045000/IRCTC UTS/UPI Bal:Rs.13013.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.50.00 UPI/YESB/460224433683/SHAMEER  CHOK Bal:Rs.13153.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.100.00 UPI/YESB/423562875714/M D JEEBRIL/U Bal:Rs.13203.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/SBIN/423495435346/MIHAL  PALAKK Bal:Rs.13303.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.96.00 UPI/YESB/423355441934/C2 CUSATRESTA Bal:Rs.13275.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.22.00 UPI/UTIB/423331479702/Google India  Bal:Rs.12886.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.22.00 UPI/ICIC/423205916378/Google India  Bal:Rs.12908.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.65.00 UPI/YESB/423138359062/IRCTC UTS/UPI Bal:Rs.12975.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/CNRB/423015805011/SANA  NOUSHAD Bal:Rs.13040.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/YESB/422966408462/SHEFEEQ P U/U Bal:Rs.13060.04 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/PYTM/404096839443/MUHAMMED NIYA Bal:Rs.2204.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.25.00 UPI/FDRL/440508831268/ABSE ABDUL VA Bal:Rs.2224.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.30.00 UPI/PUNB/440291567464/SHAANSHOUKATH Bal:Rs.2008.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/PYTM/440246736137/S and S TRADE Bal:Rs.2038.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/YESB/403612040330/SUJEET KUMAR/ Bal:Rs.2098.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.25.00 UPI/FDRL/403611953580/ABSE ABDUL VA Bal:Rs.2118.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.5.00 UPI/YESB/440160215924/LAROSA ENTERP Bal:Rs.2143.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/SIBL/403591008558/ROSHAN CYRIAC Bal:Rs.2148.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.22.00 UPI/PYTM/403500992249/SUJEET KUMAR/ Bal:Rs.2184.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/SBIN/403585856738/Roshin Roy S/ Bal:Rs.2206.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.70.00 UPI/SBIN/403585118355/Leonard  Varg Bal:Rs.2216.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.100.00 UPI/CNRB/440117780984/MUHAMMED NIHA Bal:Rs.2286.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.25.00 UPI/YESB/403574710829/SUJEET KUMAR/ Bal:Rs.2386.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.30.00 UPI/SBIN/403467195025/MIHAL  PALAKK Bal:Rs.2411.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.25.00 UPI/PYTM/440065318621/Mr PRAKASH KU Bal:Rs.2481.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.25.00 UPI/FDRL/403394381740/ABSE ABDUL VA Bal:Rs.2506.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/CNRB/403275179245/AHMAD LABEEB  Bal:Rs.2531.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.17.00 UPI/FDRL/402823643933/ABSE ABDUL VA Bal:Rs.2547.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.60.00 UPI/SBIN/401997186893/REEJA  K/UPI Bal:Rs.2549.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.12.00 UPI/PYTM/401562414976/SUJEET KUMAR/ Bal:Rs.2737.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.70.00 UPI/CNRB/401535516932/AHMAD LABEEB  Bal:Rs.2749.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.200.00 UPI/ESMF/400926996504/Mary  Joy/UPI Bal:Rs.5260.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.17.00 UPI/PYTM/400445517634/Keralashree M Bal:Rs.1321.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.50.00 UPI/PYTM/436830288556/S and S TRADE Bal:Rs.1138.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.100.00 UPI/PYTM/400246676172/BIJU/Payment  Bal:Rs.1188.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.40.00 UPI/YESB/400261877401/RAJAMANIKKAN  Bal:Rs.1238.96 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.80.00 UPI/UTIB/335273958025/AFSAL RAHMAN  Bal:Rs.4649.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.27.00 UPI/YESB/334882565406/C2 CUSATRESTA Bal:Rs.1119.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.30.00 UPI/PYTM/371360103950/The Tea Shop/ Bal:Rs.1096.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.12.00 UPI/PYTM/334754552799/Mr Ashokan K  Bal:Rs.1126.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/SBIN/371058646917/GOUTHAM  RAJE Bal:Rs.1254.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.60.00 UPI/FDRL/334440808550/PARKAFE/Payme Bal:Rs.1475.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/SBIN/334287821437/Leonard  Varg Bal:Rs.1595.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.3200.00 UPI/ESMF/334161871242/Mary  Joy/UPI Bal:Rs.4363.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.7.00 UPI/PYTM/370686618312/Mr Ashokan K  Bal:Rs.1598.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/YESB/333901779332/ABDUL  SALAM  Bal:Rs.1605.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.13.00 UPI/PYTM/333052718476/RAMESH BABU N Bal:Rs.1495.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.70.00 UPI/UTIB/333068134052/FIDHIL ASHARA Bal:Rs.1518.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/PYTM/332901578631/SUJEET KUMAR/ Bal:Rs.1588.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.100.00 UPI/PYTM/332940482146/SUJEET KUMAR/ Bal:Rs.1548.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.80.00 UPI/SBIN/332953989490/Sarath Madhav Bal:Rs.1668.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.60.00 UPI/YESB/332950238210/KREEM FOODS P Bal:Rs.1748.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.5.00 UPI/PYTM/332596068569/ABDUL RAHIMAN Bal:Rs.1858.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/FDRL/332443382989/TANYA MARIAM  Bal:Rs.1873.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.150.00 UPI/CNRB/332197092029/AHMAD LABEEB  Bal:Rs.1853.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.150.00 UPI/CNRB/368792655995/AHMAD LABEEB  Bal:Rs.1953.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.200.00 UPI/ESMF/332050630905/Mary  Joy/UPI Bal:Rs.1973.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.49.00 UPI/CNRB/331745183972/MARY SINI/Pay Bal:Rs.2454.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.18.00 UPI/UTIB/331733975971/AXIS BANK LTD Bal:Rs.2523.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.47.00 UPI/YESB/331774278736/ABDUL  SALAM  Bal:Rs.2437.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.20.00 UPI/PYTM/331797208496/JITHINA/Payme Bal:Rs.2484.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.87.00 UPI/CNRB/331642070238/MATTANCHERRY  Bal:Rs.2504.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.5.00 UPI/YESB/331458853287/ABDUL  SALAM  Bal:Rs.5933.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.10.00 UPI/JAKA/331310420613/SAJAD HUSSAIN Bal:Rs.5948.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.2770.00 UPI/SBIN/331274761601/SAFVAN  IBRAH Bal:Rs.5963.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c X3059 DEBIT:Rs.176.00 UPI/CNRB/331173924507/MARY SINI/Pay Bal:Rs.8733.46 Block A/c?call 18004251809/SMS BLK&lt;full A/c&gt;to 9840777222-South Indian Bank</t>
+  </si>
+  <si>
+    <t>JIO MART</t>
+  </si>
+  <si>
+    <t>Google India</t>
+  </si>
+  <si>
+    <t>Shadin Hafizu</t>
+  </si>
+  <si>
+    <t>SAINUDHEEN  A</t>
+  </si>
+  <si>
+    <t>C1 CUSAT REST</t>
+  </si>
+  <si>
+    <t>Indian Railwa</t>
+  </si>
+  <si>
+    <t>Swiggy Limite</t>
+  </si>
+  <si>
+    <t>MOHAMED SAFEE</t>
+  </si>
+  <si>
+    <t>GAYATHRI</t>
+  </si>
+  <si>
+    <t>Ishak V T</t>
+  </si>
+  <si>
+    <t>AKASH  K</t>
+  </si>
+  <si>
+    <t>Mr HAIMEN  DC</t>
+  </si>
+  <si>
+    <t>AKSHAY GOPAKU</t>
+  </si>
+  <si>
+    <t>BIBIN MILLENT</t>
+  </si>
+  <si>
+    <t>Mavinchoode 3</t>
+  </si>
+  <si>
+    <t>AKASH K</t>
+  </si>
+  <si>
+    <t>ROSE  MARIA</t>
+  </si>
+  <si>
+    <t>ABDUL  SALAM</t>
+  </si>
+  <si>
+    <t>KALPAKA TRANS</t>
+  </si>
+  <si>
+    <t>NEMA  FATHIMA</t>
+  </si>
+  <si>
+    <t>RISHI KRISHNA</t>
+  </si>
+  <si>
+    <t>VISHNU P RAJA</t>
+  </si>
+  <si>
+    <t>Leonard  Varg</t>
+  </si>
+  <si>
+    <t>C2 CUSATRESTA</t>
+  </si>
+  <si>
+    <t>JALEEL K H</t>
+  </si>
+  <si>
+    <t>ABDUL SALAM K</t>
+  </si>
+  <si>
+    <t>AVANEESH P A</t>
+  </si>
+  <si>
+    <t>MP MART LLP B</t>
+  </si>
+  <si>
+    <t>ROMAL  JOSBIN</t>
+  </si>
+  <si>
+    <t>ARSHAD</t>
+  </si>
+  <si>
+    <t>ABSE ABDUL VA</t>
+  </si>
+  <si>
+    <t>SHAMEER  CHOK</t>
+  </si>
+  <si>
+    <t>M D JEEBRIL</t>
+  </si>
+  <si>
+    <t>MUHAMMED NIYA</t>
+  </si>
+  <si>
+    <t>SHAANSHOUKATH</t>
+  </si>
+  <si>
+    <t>S and S TRADE</t>
+  </si>
+  <si>
+    <t>LAROSA ENTERP</t>
+  </si>
+  <si>
+    <t>ROSHAN CYRIAC</t>
+  </si>
+  <si>
+    <t>MUHAMMED NIHA</t>
+  </si>
+  <si>
+    <t>Mr PRAKASH KU</t>
+  </si>
+  <si>
+    <t>AHMAD LABEEB</t>
+  </si>
+  <si>
+    <t>REEJA  K</t>
+  </si>
+  <si>
+    <t>Mary  Joy</t>
+  </si>
+  <si>
+    <t>Keralashree M</t>
+  </si>
+  <si>
+    <t>RAJAMANIKKAN</t>
+  </si>
+  <si>
+    <t>AFSAL RAHMAN</t>
+  </si>
+  <si>
+    <t>Mr Ashokan K</t>
+  </si>
+  <si>
+    <t>GOUTHAM  RAJE</t>
+  </si>
+  <si>
+    <t>PARKAFE</t>
+  </si>
+  <si>
+    <t>RAMESH BABU N</t>
+  </si>
+  <si>
+    <t>FIDHIL ASHARA</t>
+  </si>
+  <si>
+    <t>Sarath Madhav</t>
+  </si>
+  <si>
+    <t>KREEM FOODS P</t>
+  </si>
+  <si>
+    <t>ABDUL RAHIMAN</t>
+  </si>
+  <si>
+    <t>TANYA MARIAM</t>
+  </si>
+  <si>
+    <t>MARY SINI</t>
+  </si>
+  <si>
+    <t>AXIS BANK LTD</t>
+  </si>
+  <si>
+    <t>JITHINA</t>
+  </si>
+  <si>
+    <t>MATTANCHERRY</t>
+  </si>
+  <si>
+    <t>SAJAD HUSSAIN</t>
+  </si>
+  <si>
+    <t>SAFVAN  IBRAH</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 540.00, A/c No. XX059 on 2025-05-15 09.42.11 UPI Ref No. 162360611494 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 6.00, A/c No. XX059 on 2025-05-06 20.52.35 UPI Ref No. 549209304901 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 240.00, A/c No. XX059 on 2025-05-03 23.06.35 UPI Ref No. 512316990685 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 100.00, A/c No. XX059 on 2025-04-16 12.55.55 UPI Ref No. 510643114404 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 66.00, A/c No. XX059 on 2025-04-08 20.00.17 UPI Ref No. 509895954242 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 30.00, A/c No. XX059 on 2025-04-07 02.36.29 UPI Ref No. 509717934785 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 1150.00, A/c No. XX059 on 2025-03-23 00.23.47 UPI Ref No. 544831141451 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 140.00, A/c No. XX059 on 2025-03-08 23.17.58 UPI Ref No. 506771811042 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 30.00, A/c No. XX059 on 2025-03-08 23.17.46 UPI Ref No. 506771778176 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 30.00, A/c No. XX059 on 2025-03-08 23.17.24 UPI Ref No. 506771756678 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 20.00, A/c No. XX059 on 2025-02-21 18.16.37 UPI Ref No. 100381880706 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 30.00, A/c No. XX059 on 2025-02-19 17.29.51 UPI Ref No. 505052848954 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 20.00, A/c No. XX059 on 2025-02-03 20.38.57 UPI Ref No. 503484642527 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 20.00, A/c No. XX059 on 2025-02-03 20.38.38 UPI Ref No. 503403439470 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 500.00, A/c No. XX059 on 2025-01-26 18.31.27 UPI Ref No. 654343762920 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 206.25, A/c No. XX059 on 2025-01-23 16.38.21 UPI Ref No. 502314475367 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 148.00, A/c No. XX059 on 2024-12-26 08.23.54 UPI Ref No. 436196809547 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 20.00, A/c No. XX059 on 2024-12-26 08.12.53 UPI Ref No. 436196500081 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 7.00, A/c No. XX059 on 2024-12-08 13.04.46 UPI Ref No. 434399342919 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 50.00, A/c No. XX059 on 2024-12-01 08.19.46 UPI Ref No. 470239288626 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 39.66, A/c No. XX059 on 2024-11-28 00.09.36 UPI Ref No. 469965884741 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 3500.00, A/c No. XX059 on 2024-11-10 14.19.51 UPI Ref No. 863822523607 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 34.00, A/c No. XX059 on 2024-10-12 11.47.36 UPI Ref No. 428622605005 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 3500.00, A/c No. XX059 on 2024-10-04 21.16.09 UPI Ref No. 427889762227 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 3000.00, A/c No. XX059 on 2024-09-27 21.16.03 UPI Ref No. 427194705462 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 1500.00, A/c No. XX059 on 2024-09-22 14.46.06 UPI Ref No. 426674914878 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 172.00, A/c No. XX059 on 2024-09-12 21.10.19 UPI Ref No. 425651991122 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Credit:Rs. 1000.00, A/c No. XX059 on 2024-09-08 21.20.35 UPI Ref No. 425268699120 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>CREDIT</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 75.00, A/c No. XX059 on 2025-05-17 11.35.44 UPI Ref No. 513790184764 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 540.90, A/c No. XX059 on 2025-05-15 09.39.25 UPI Ref No. 513568982781 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 40.00, A/c No. XX059 on 2025-05-15 09.30.13 UPI Ref No. 513568443202 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 100.00, A/c No. XX059 on 2025-05-08 13.27.54 UPI Ref No. 512805384242 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 50.00, A/c No. XX059 on 2025-05-07 16.58.28 UPI Ref No. 549351364210 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 105.00, A/c No. XX059 on 2025-05-06 19.54.27 UPI Ref No. 512638690911 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 45.00, A/c No. XX059 on 2025-05-06 12.22.37 UPI Ref No. 512619522924 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 93.00, A/c No. XX059 on 2025-05-05 12.36.18 UPI Ref No. 549155830074 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 10.00, A/c No. XX059 on 2025-05-01 13.29.33 UPI Ref No. 512192533605 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 230.00, A/c No. XX059 on 2025-04-25 13.24.45 UPI Ref No. 511546376094 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 200.88, A/c No. XX059 on 2025-04-25 11.19.08 UPI Ref No. 511540965902 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 65.00, A/c No. XX059 on 2025-04-12 06.48.22 UPI Ref No. 510287696316 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 10.00, A/c No. XX059 on 2025-04-08 12.16.33 UPI Ref No. 509890451454 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 150.00, A/c No. XX059 on 2025-03-28 13.45.32 UPI Ref No. 508763205837 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 85.00, A/c No. XX059 on 2025-03-24 19.08.26 UPI Ref No. 508319600606 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 105.00, A/c No. XX059 on 2025-03-23 18.23.53 UPI Ref No. 544824901842 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 50.00, A/c No. XX059 on 2025-03-16 13.40.38 UPI Ref No. 544178374947 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 60.00, A/c No. XX059 on 2025-03-15 12.59.52 UPI Ref No. 507448369107 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 980.00, A/c No. XX059 on 2025-03-13 08.49.51 UPI Ref No. 507237856648 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 1452.00, A/c No. XX059 on 2025-03-08 23.11.03 UPI Ref No. 506732696643 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 18.00, A/c No. XX059 on 2025-03-07 22.40.17 UPI Ref No. 506645536192 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 28.33, A/c No. XX059 on 2025-03-06 21.28.34 UPI Ref No. 101059178060 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 3250.00, A/c No. XX059 on 2025-03-06 08.45.55 UPI Ref No. 506539123537 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 255.00, A/c No. XX059 on 2025-02-28 17.16.34 UPI Ref No. 505947119294 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 48.00, A/c No. XX059 on 2025-02-28 07.15.05 UPI Ref No. 505911866474 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 12.00, A/c No. XX059 on 2025-02-24 23.11.54 UPI Ref No. 542161036690 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 60.00, A/c No. XX059 on 2025-02-21 14.25.26 UPI Ref No. 505214963622 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 15.00, A/c No. XX059 on 2025-02-20 10.28.15 UPI Ref No. 541709141275 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 90.00, A/c No. XX059 on 2025-02-13 15.00.44 UPI Ref No. 504489238199 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 60.00, A/c No. XX059 on 2025-02-07 18.13.41 UPI Ref No. 503858947936 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 175.00, A/c No. XX059 on 2025-02-04 23.35.56 UPI Ref No. 503536735392 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 35.00, A/c No. XX059 on 2025-02-04 21.45.45 UPI Ref No. 540134824072 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 38.00, A/c No. XX059 on 2025-02-03 18.29.23 UPI Ref No. 503486931661 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 40.00, A/c No. XX059 on 2025-01-24 11.10.16 UPI Ref No. 502434568425 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 36.37, A/c No. XX059 on 2025-01-22 19.02.37 UPI Ref No. 538866028013 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 55.00, A/c No. XX059 on 2025-01-12 23.36.35 UPI Ref No. 501210825163 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 2655.00, A/c No. XX059 on 2025-01-12 19.17.08 UPI Ref No. 501296426060 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 50.00, A/c No. XX059 on 2025-01-10 12.11.21 UPI Ref No. 537676334005 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 20.00, A/c No. XX059 on 2025-01-07 13.15.55 UPI Ref No. 500750438953 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 65.00, A/c No. XX059 on 2024-12-31 14.25.11 UPI Ref No. 436688901359 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 48.00, A/c No. XX059 on 2024-12-27 17.11.30 UPI Ref No. 436286432392 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 100.00, A/c No. XX059 on 2024-12-21 08.20.26 UPI Ref No. 472228088407 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 24.00, A/c No. XX059 on 2024-12-21 06.59.46 UPI Ref No. 435616604031 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 22.00, A/c No. XX059 on 2024-12-16 18.07.27 UPI Ref No. 435116945901 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 13.33, A/c No. XX059 on 2024-12-08 13.01.28 UPI Ref No. 434311840688 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 1890.00, A/c No. XX059 on 2024-12-06 21.36.43 UPI Ref No. 434140238243 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 127.00, A/c No. XX059 on 2024-11-28 12.51.31 UPI Ref No. 433390888367 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 147.00, A/c No. XX059 on 2024-11-27 23.51.05 UPI Ref No. 433232586093 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 3.08, A/c No. XX059 on 2024-11-24 19.07.30 UPI Ref No. 432910278149 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 20.00, A/c No. XX059 on 2024-11-24 03.53.41 UPI Ref No. 432982289043 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 170.00, A/c No. XX059 on 2024-11-24 03.52.31 UPI Ref No. 432943600714 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 10.00, A/c No. XX059 on 2024-11-15 13.47.18 UPI Ref No. 432041390851 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 8.00, A/c No. XX059 on 2024-11-15 09.16.18 UPI Ref No. 468623332583 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 40.00, A/c No. XX059 on 2024-11-14 16.23.24 UPI Ref No. 431999120100 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 20.00, A/c No. XX059 on 2024-11-12 14.10.38 UPI Ref No. 431798587461 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 1042.00, A/c No. XX059 on 2024-11-11 08.25.14 UPI Ref No. 431623179929 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 116.00, A/c No. XX059 on 2024-11-10 20.49.02 UPI Ref No. 431515093095 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 20.00, A/c No. XX059 on 2024-11-08 10.14.22 UPI Ref No. 467900376048 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 15.00, A/c No. XX059 on 2024-11-07 11.20.37 UPI Ref No. 431224708899 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 350.00, A/c No. XX059 on 2024-11-07 09.07.14 UPI Ref No. 431233157396 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 20.00, A/c No. XX059 on 2024-11-06 10.55.51 UPI Ref No. 467733554367 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 15.00, A/c No. XX059 on 2024-11-05 17.30.15 UPI Ref No. 431052196448 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 20.00, A/c No. XX059 on 2024-11-05 11.03.02 UPI Ref No. 431028440494 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 100.00, A/c No. XX059 on 2024-10-06 17.56.01 UPI Ref No. 428002453180 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 15.00, A/c No. XX059 on 2024-10-04 11.23.55 UPI Ref No. 427807995236 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 9.00, A/c No. XX059 on 2024-10-02 17.50.01 UPI Ref No. 427694580608 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 20.00, A/c No. XX059 on 2024-10-01 16.18.29 UPI Ref No. 427533579238 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 25.00, A/c No. XX059 on 2024-10-01 10.56.42 UPI Ref No. 464174174439 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 38.00, A/c No. XX059 on 2024-09-30 10.09.13 UPI Ref No. 427415602527 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 480.90, A/c No. XX059 on 2024-09-27 09.11.25 UPI Ref No. 427117826747 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 10.00, A/c No. XX059 on 2024-09-26 17.57.36 UPI Ref No. 427094308323 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 15.00, A/c No. XX059 on 2024-09-25 10.51.41 UPI Ref No. 426952206700 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 30.00, A/c No. XX059 on 2024-09-24 10.56.21 UPI Ref No. 426853295738 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 45.00, A/c No. XX059 on 2024-09-23 09.40.11 UPI Ref No. 426733434338 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 70.00, A/c No. XX059 on 2024-09-22 13.56.45 UPI Ref No. 426695098291 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 55.00, A/c No. XX059 on 2024-09-18 15.29.38 UPI Ref No. 426200720296 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 22.00, A/c No. XX059 on 2024-09-16 08.48.14 UPI Ref No. 426061519046 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 22.00, A/c No. XX059 on 2024-09-15 10.26.51 UPI Ref No. 425912718767 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 36.00, A/c No. XX059 on 2024-09-13 10.02.28 UPI Ref No. 425716680905 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 65.00, A/c No. XX059 on 2024-09-13 06.29.25 UPI Ref No. 425709850517 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 20.00, A/c No. XX059 on 2024-09-11 21.51.48 UPI Ref No. 462160969985 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 1928.00, A/c No. XX059 on 2024-09-11 12.47.46 UPI Ref No. 425516993982 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 179.00, A/c No. XX059 on 2024-09-07 22.57.19 UPI Ref No. 425146062318 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 1.08, A/c No. XX059 on 2024-09-07 11.33.47 UPI Ref No. 425107125363 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 75.00, A/c No. XX059 on 2024-09-07 10.23.39 UPI Ref No. 425145939164 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>A/c Debit:Rs. 18.00, A/c No. XX059 on 2024-09-05 10.09.26 UPI Ref No. 424994642618 -South Indian Bank</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 540.00 Info: UPI/SBIN/162360611494/ABDUL MAJEED . Final balance is Rs 20424.88-South Indian Bank</t>
+  </si>
+  <si>
+    <t>162360611494</t>
+  </si>
+  <si>
+    <t>ABDUL MAJEED</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 60.00 Info: UPI/FDRL/512374933531/FINSHA P/UPI. Final balance is Rs 20546.48-South Indian Bank</t>
+  </si>
+  <si>
+    <t>512374933531</t>
+  </si>
+  <si>
+    <t>FINSHA P/UPI</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 1000.00 Info: UPI/SBIN/656565425760/ABDUL MAJEED . Final balance is Rs 20861.26-South Indian Bank</t>
+  </si>
+  <si>
+    <t>656565425760</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 80.00 Info: UPI/FDRL/103029971875/ABSE ABDUL VA. Final balance is Rs 19860.15-South Indian Bank</t>
+  </si>
+  <si>
+    <t>103029971875</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 91.00 Info: UPI/PUNB/102835200756/SACHIN H/UPI. Final balance is Rs 21841.75-South Indian Bank</t>
+  </si>
+  <si>
+    <t>102835200756</t>
+  </si>
+  <si>
+    <t>SACHIN H/UPI</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 140.00 Info: UPI/SBIN/506771811042/MIHAL  PALAKK. Final balance is Rs 14987.49-South Indian Bank</t>
+  </si>
+  <si>
+    <t>506771811042</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 30.00 Info: UPI/SBIN/506771778176/MIHAL  PALAKK. Final balance is Rs 14847.49-South Indian Bank</t>
+  </si>
+  <si>
+    <t>506771778176</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 9.57 Info: UPI/SBIN/506771769226/Manukrishnan . Final balance is Rs 14817.49-South Indian Bank</t>
+  </si>
+  <si>
+    <t>506771769226</t>
+  </si>
+  <si>
+    <t>Manukrishnan</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 30.00 Info: UPI/SBIN/506771756678/Manukrishnan . Final balance is Rs 14798.35-South Indian Bank</t>
+  </si>
+  <si>
+    <t>506771756678</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 9.57 Info: UPI/CNRB/506721696745/SANA  NOUSHAD. Final balance is Rs 14358.35-South Indian Bank</t>
+  </si>
+  <si>
+    <t>506721696745</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 240.00 Info: UPI/SBIN/506771635786/Rithuparna J . Final balance is Rs 14120.06-South Indian Bank</t>
+  </si>
+  <si>
+    <t>506771635786</t>
+  </si>
+  <si>
+    <t>Rithuparna J</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 15.00 Info: UPI/SBIN/543190212360/MIHAL  PALAKK. Final balance is Rs 15346.06-South Indian Bank</t>
+  </si>
+  <si>
+    <t>543190212360</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 3500.00 Info: UPI/SBIN/784980585689/ABDUL MAJEED . Final balance is Rs 19667.78-South Indian Bank</t>
+  </si>
+  <si>
+    <t>784980585689</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 34.00 Info: UPI/SBIN/502146622709/ADARSH  VISHW. Final balance is Rs 13229.23-South Indian Bank</t>
+  </si>
+  <si>
+    <t>502146622709</t>
+  </si>
+  <si>
+    <t>ADARSH  VISHW</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 3500.00 Info: UPI/SBIN/786193329647/ABDUL MAJEED . Final balance is Rs 14341.09-South Indian Bank</t>
+  </si>
+  <si>
+    <t>786193329647</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 20.00 Info: UPI/REVR/500750438953/SHEFEEQ P U/U. Final balance is Rs 13603.59-South Indian Bank</t>
+  </si>
+  <si>
+    <t>500750438953</t>
+  </si>
+  <si>
+    <t>SHEFEEQ P U/U</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 3500.00 Info: UPI/SBIN/206717054514/ABDUL MAJEED . Final balance is Rs 18168.94-South Indian Bank</t>
+  </si>
+  <si>
+    <t>206717054514</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 90.00 Info: UPI/FDRL/433329204310/MOHAMED JASEE. Final balance is Rs 14928.94-South Indian Bank</t>
+  </si>
+  <si>
+    <t>433329204310</t>
+  </si>
+  <si>
+    <t>MOHAMED JASEE</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 7.00 Info: UPI/SBIN/433240496358/Firoz  Zaman/. Final balance is Rs 14956.03-South Indian Bank</t>
+  </si>
+  <si>
+    <t>433240496358</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 14.00 Info: UPI/CNRB/469540954450/SANA  NOUSHAD. Final balance is Rs 15070.28-South Indian Bank</t>
+  </si>
+  <si>
+    <t>469540954450</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 1000.00 Info: UPI/SBIN/511373401545/ABDUL MAJEED . Final balance is Rs 15434.86-South Indian Bank</t>
+  </si>
+  <si>
+    <t>511373401545</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 10.00 Info: UPI/CNRB/432442617183/ASIM  SHANU/U. Final balance is Rs 15138.76-South Indian Bank</t>
+  </si>
+  <si>
+    <t>432442617183</t>
+  </si>
+  <si>
+    <t>ASIM  SHANU/U</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 28.00 Info: UPI/PUNB/431540084204/SACHIN H/UPI. Final balance is Rs 18615.05-South Indian Bank</t>
+  </si>
+  <si>
+    <t>431540084204</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs 4000.00 Info: UPI/SBIN/664709674946/ABDUL MAJEED . Final balance is Rs 19214.80-South Indian Bank</t>
+  </si>
+  <si>
+    <t>664709674946</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.3500.00 Info: UPI/SBIN/427889762227/ABDUL MAJEED . Final balance is Rs.18931.49-South Indian Bank</t>
+  </si>
+  <si>
+    <t>427889762227</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.3000.00 Info: UPI/SBIN/427194705462/ABDUL MAJEED . Final balance is Rs.18626.49-South Indian Bank</t>
+  </si>
+  <si>
+    <t>427194705462</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.172.00 Info: UPI/SBIN/425651991122/MIHAL  PALAKK. Final balance is Rs.13097.39-South Indian Bank</t>
+  </si>
+  <si>
+    <t>425651991122</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.1000.00 Info: UPI/SBIN/425268699120/ABDUL MAJEED . Final balance is Rs.15255.39-South Indian Bank</t>
+  </si>
+  <si>
+    <t>425268699120</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.1000.00 Info: UPI/SBIN/424131879882/ABDUL MAJEED . Final balance is Rs.12886.37-South Indian Bank</t>
+  </si>
+  <si>
+    <t>424131879882</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.5.00 Info: UPI/UTIB/423613343109/GOOGLE INDIA . Final balance is Rs.13027.37-South Indian Bank</t>
+  </si>
+  <si>
+    <t>423613343109</t>
+  </si>
+  <si>
+    <t>GOOGLE INDIA</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.48.00 Info: UPI/PUNB/423356505716/ASHISH P S/UP. Final balance is Rs.13323.04-South Indian Bank</t>
+  </si>
+  <si>
+    <t>423356505716</t>
+  </si>
+  <si>
+    <t>ASHISH P S/UP</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.20.00 Info: UPI/SBIN/403762806362/MIHAL  PALAKK. Final balance is Rs.5503.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>403762806362</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.3500.00 Info: UPI/SBIN/403641891161/ABDUL MAJEED . Final balance is Rs.5508.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>403641891161</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.10.00 Info: UPI/SBIN/440132598232/Roshin Roy S/. Final balance is Rs.2158.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>440132598232</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.15.00 Info: UPI/SBIN/401997281496/Rithuparna J . Final balance is Rs.2564.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>401997281496</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.11.00 Info: UPI/UTIB/401871979183/GOOGLEPAY/UPI. Final balance is Rs.2759.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>401871979183</t>
+  </si>
+  <si>
+    <t>GOOGLEPAY/UPI</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.5.00 Info: UPI/UTIB/401871976555/GOOGLEPAY/UPI. Final balance is Rs.2764.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>401871976555</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.500.00 Info: UPI/SBIN/401759078235/ABDUL MAJEED . Final balance is Rs.3227.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>401759078235</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.10.00 Info: UPI/SBIN/401371971722/MIHAL  PALAKK. Final balance is Rs.2781.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>401371971722</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.4.00 Info: UPI/SBIN/436979803886/MIHAL  PALAKK. Final balance is Rs.1338.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>436979803886</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.200.00 Info: UPI/PUNB/400310434250/THASNIMOL P/U. Final balance is Rs.1334.96-South Indian Bank</t>
+  </si>
+  <si>
+    <t>400310434250</t>
+  </si>
+  <si>
+    <t>THASNIMOL P/U</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.50.00 Info: UPI/CNRB/332927927773/MIDHUN M/UPI. Final balance is Rs.1598.46-South Indian Bank</t>
+  </si>
+  <si>
+    <t>332927927773</t>
+  </si>
+  <si>
+    <t>MIDHUN M/UPI</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.20.00 Info: UPI/CNRB/332362407072/AHMAD LABEEB . Final balance is Rs.1863.46-South Indian Bank</t>
+  </si>
+  <si>
+    <t>332362407072</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.150.00 Info: UPI/CNRB/332193654688/AHMAD LABEEB . Final balance is Rs.2253.46-South Indian Bank</t>
+  </si>
+  <si>
+    <t>332193654688</t>
+  </si>
+  <si>
+    <t>Dear Customer, Your A/c X3059 is credited with Rs.104.00 Info: UPI/SBIN/331731202122/Afnash Ali P/. Final balance is Rs.2541.46-South Indian Bank</t>
+  </si>
+  <si>
+    <t>331731202122</t>
   </si>
 </sst>
 </file>
@@ -4020,10 +5310,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4338,7 +5641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846199F2-8382-44B3-BC60-3A49979AC007}">
-  <dimension ref="A1:G689"/>
+  <dimension ref="A1:G997"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -17737,6 +19040,6400 @@
         <v>119</v>
       </c>
     </row>
+    <row r="690" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B690">
+        <v>75</v>
+      </c>
+      <c r="C690">
+        <v>20349.88</v>
+      </c>
+      <c r="D690">
+        <v>513790184764</v>
+      </c>
+      <c r="E690" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F690" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G690" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A691" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B691" s="4">
+        <v>75</v>
+      </c>
+      <c r="C691" s="5">
+        <v>20349.88</v>
+      </c>
+      <c r="D691" s="6">
+        <v>513790184764</v>
+      </c>
+      <c r="E691" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F691" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G691" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A692" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B692" s="4">
+        <v>100</v>
+      </c>
+      <c r="C692" s="5">
+        <v>20942.48</v>
+      </c>
+      <c r="D692" s="6">
+        <v>512805384242</v>
+      </c>
+      <c r="E692" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F692" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G692" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A693" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B693" s="4">
+        <v>40</v>
+      </c>
+      <c r="C693" s="5">
+        <v>20425.78</v>
+      </c>
+      <c r="D693" s="6">
+        <v>513568443202</v>
+      </c>
+      <c r="E693" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F693" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G693" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A694" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B694" s="4">
+        <v>63</v>
+      </c>
+      <c r="C694" s="5">
+        <v>20879.48</v>
+      </c>
+      <c r="D694" s="6">
+        <v>512822945838</v>
+      </c>
+      <c r="E694" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F694" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G694" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A695" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B695" s="4">
+        <v>540.9</v>
+      </c>
+      <c r="C695" s="5">
+        <v>19884.88</v>
+      </c>
+      <c r="D695" s="6">
+        <v>513568982781</v>
+      </c>
+      <c r="E695" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F695" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G695" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A696" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B696" s="4">
+        <v>27</v>
+      </c>
+      <c r="C696" s="5">
+        <v>21042.48</v>
+      </c>
+      <c r="D696" s="6">
+        <v>549323958969</v>
+      </c>
+      <c r="E696" s="7" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F696" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G696" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A697" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B697" s="4">
+        <v>50</v>
+      </c>
+      <c r="C697" s="5">
+        <v>21069.48</v>
+      </c>
+      <c r="D697" s="6">
+        <v>549351364210</v>
+      </c>
+      <c r="E697" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F697" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G697" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A698" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B698" s="4">
+        <v>230</v>
+      </c>
+      <c r="C698" s="5">
+        <v>20064.48</v>
+      </c>
+      <c r="D698" s="6">
+        <v>511546376094</v>
+      </c>
+      <c r="E698" s="7" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F698" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G698" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A699" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B699" s="4">
+        <v>40</v>
+      </c>
+      <c r="C699" s="5">
+        <v>20680.36</v>
+      </c>
+      <c r="D699" s="6">
+        <v>511165775193</v>
+      </c>
+      <c r="E699" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F699" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G699" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A700" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B700" s="4">
+        <v>72.64</v>
+      </c>
+      <c r="C700" s="5">
+        <v>19861.259999999998</v>
+      </c>
+      <c r="D700" s="6">
+        <v>511043232351</v>
+      </c>
+      <c r="E700" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F700" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G700" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A701" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B701" s="4">
+        <v>23</v>
+      </c>
+      <c r="C701" s="5">
+        <v>19985.150000000001</v>
+      </c>
+      <c r="D701" s="6">
+        <v>510778891856</v>
+      </c>
+      <c r="E701" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F701" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G701" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="702" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A702" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B702" s="4">
+        <v>90</v>
+      </c>
+      <c r="C702" s="5">
+        <v>19690.150000000001</v>
+      </c>
+      <c r="D702" s="6">
+        <v>510669306846</v>
+      </c>
+      <c r="E702" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F702" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G702" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="703" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A703" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B703" s="4">
+        <v>65</v>
+      </c>
+      <c r="C703" s="5">
+        <v>19790.150000000001</v>
+      </c>
+      <c r="D703" s="6">
+        <v>510287696316</v>
+      </c>
+      <c r="E703" s="7" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F703" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G703" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="704" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A704" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B704" s="4">
+        <v>96</v>
+      </c>
+      <c r="C704" s="5">
+        <v>21825.75</v>
+      </c>
+      <c r="D704" s="6">
+        <v>509925087542</v>
+      </c>
+      <c r="E704" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F704" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G704" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="705" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A705" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B705" s="4">
+        <v>75</v>
+      </c>
+      <c r="C705" s="5">
+        <v>22152.65</v>
+      </c>
+      <c r="D705" s="6">
+        <v>509612622844</v>
+      </c>
+      <c r="E705" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F705" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G705" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="706" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A706" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B706" s="4">
+        <v>150</v>
+      </c>
+      <c r="C706" s="5">
+        <v>20145.650000000001</v>
+      </c>
+      <c r="D706" s="6">
+        <v>508763205837</v>
+      </c>
+      <c r="E706" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F706" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G706" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="707" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A707" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B707" s="4">
+        <v>30</v>
+      </c>
+      <c r="C707" s="5">
+        <v>16685.650000000001</v>
+      </c>
+      <c r="D707" s="6">
+        <v>544792370370</v>
+      </c>
+      <c r="E707" s="7" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F707" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G707" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="708" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A708" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B708" s="4">
+        <v>75</v>
+      </c>
+      <c r="C708" s="5">
+        <v>13980.92</v>
+      </c>
+      <c r="D708" s="6">
+        <v>507855022919</v>
+      </c>
+      <c r="E708" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F708" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G708" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="709" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A709" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B709" s="4">
+        <v>60</v>
+      </c>
+      <c r="C709" s="5">
+        <v>14427.92</v>
+      </c>
+      <c r="D709" s="6">
+        <v>507448369107</v>
+      </c>
+      <c r="E709" s="7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F709" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G709" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="710" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A710" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B710" s="4">
+        <v>100</v>
+      </c>
+      <c r="C710" s="5">
+        <v>14487.92</v>
+      </c>
+      <c r="D710" s="6">
+        <v>507410313412</v>
+      </c>
+      <c r="E710" s="7" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F710" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G710" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="711" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A711" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B711" s="4">
+        <v>25</v>
+      </c>
+      <c r="C711" s="5">
+        <v>14587.92</v>
+      </c>
+      <c r="D711" s="6">
+        <v>507289848857</v>
+      </c>
+      <c r="E711" s="7" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F711" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G711" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="712" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A712" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B712" s="4">
+        <v>2997</v>
+      </c>
+      <c r="C712" s="5">
+        <v>14702.92</v>
+      </c>
+      <c r="D712" s="6">
+        <v>507238033790</v>
+      </c>
+      <c r="E712" s="7" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F712" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G712" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="713" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A713" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B713" s="4">
+        <v>3250</v>
+      </c>
+      <c r="C713" s="5">
+        <v>15423.89</v>
+      </c>
+      <c r="D713" s="6">
+        <v>506539123537</v>
+      </c>
+      <c r="E713" s="7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F713" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G713" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="714" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A714" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B714" s="4">
+        <v>40</v>
+      </c>
+      <c r="C714" s="5">
+        <v>15450.79</v>
+      </c>
+      <c r="D714" s="6">
+        <v>504391676575</v>
+      </c>
+      <c r="E714" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F714" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G714" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="715" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A715" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B715" s="4">
+        <v>74.989999999999995</v>
+      </c>
+      <c r="C715" s="5">
+        <v>15490.79</v>
+      </c>
+      <c r="D715" s="6">
+        <v>504381457636</v>
+      </c>
+      <c r="E715" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F715" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G715" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="716" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A716" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B716" s="4">
+        <v>20</v>
+      </c>
+      <c r="C716" s="5">
+        <v>15595.78</v>
+      </c>
+      <c r="D716" s="6">
+        <v>540723124345</v>
+      </c>
+      <c r="E716" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F716" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G716" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="717" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A717" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B717" s="4">
+        <v>3376</v>
+      </c>
+      <c r="C717" s="5">
+        <v>16094.78</v>
+      </c>
+      <c r="D717" s="6">
+        <v>503773856454</v>
+      </c>
+      <c r="E717" s="7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F717" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G717" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="718" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A718" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B718" s="4">
+        <v>65</v>
+      </c>
+      <c r="C718" s="5">
+        <v>13265.78</v>
+      </c>
+      <c r="D718" s="6">
+        <v>502314653274</v>
+      </c>
+      <c r="E718" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F718" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G718" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="719" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A719" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B719" s="4">
+        <v>10</v>
+      </c>
+      <c r="C719" s="5">
+        <v>13617.19</v>
+      </c>
+      <c r="D719" s="6">
+        <v>501841012637</v>
+      </c>
+      <c r="E719" s="7" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F719" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G719" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="720" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A720" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B720" s="4">
+        <v>3</v>
+      </c>
+      <c r="C720" s="5">
+        <v>13682.19</v>
+      </c>
+      <c r="D720" s="6">
+        <v>501637054557</v>
+      </c>
+      <c r="E720" s="7" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F720" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G720" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="721" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A721" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B721" s="4">
+        <v>370.9</v>
+      </c>
+      <c r="C721" s="5">
+        <v>13715.19</v>
+      </c>
+      <c r="D721" s="6">
+        <v>501486312493</v>
+      </c>
+      <c r="E721" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F721" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G721" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A722" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B722" s="4">
+        <v>20</v>
+      </c>
+      <c r="C722" s="5">
+        <v>14116.09</v>
+      </c>
+      <c r="D722" s="6">
+        <v>501306053528</v>
+      </c>
+      <c r="E722" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F722" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G722" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="723" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A723" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B723" s="4">
+        <v>100</v>
+      </c>
+      <c r="C723" s="5">
+        <v>14136.09</v>
+      </c>
+      <c r="D723" s="6">
+        <v>501210844126</v>
+      </c>
+      <c r="E723" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F723" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G723" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="724" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A724" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B724" s="4">
+        <v>20</v>
+      </c>
+      <c r="C724" s="5">
+        <v>13583.59</v>
+      </c>
+      <c r="D724" s="6">
+        <v>500750608612</v>
+      </c>
+      <c r="E724" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F724" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G724" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="725" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A725" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B725" s="4">
+        <v>33</v>
+      </c>
+      <c r="C725" s="5">
+        <v>13970.85</v>
+      </c>
+      <c r="D725" s="6">
+        <v>436522933901</v>
+      </c>
+      <c r="E725" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F725" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G725" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="726" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A726" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B726" s="4">
+        <v>20</v>
+      </c>
+      <c r="C726" s="5">
+        <v>14920.95</v>
+      </c>
+      <c r="D726" s="6">
+        <v>434519395558</v>
+      </c>
+      <c r="E726" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F726" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G726" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="727" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A727" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B727" s="4">
+        <v>1890</v>
+      </c>
+      <c r="C727" s="5">
+        <v>14973.61</v>
+      </c>
+      <c r="D727" s="6">
+        <v>434140238243</v>
+      </c>
+      <c r="E727" s="7" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F727" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G727" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="728" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A728" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B728" s="4">
+        <v>1000</v>
+      </c>
+      <c r="C728" s="5">
+        <v>16863.61</v>
+      </c>
+      <c r="D728" s="6">
+        <v>434140272870</v>
+      </c>
+      <c r="E728" s="7" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F728" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G728" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A729" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B729" s="4">
+        <v>3345</v>
+      </c>
+      <c r="C729" s="5">
+        <v>17823.939999999999</v>
+      </c>
+      <c r="D729" s="6">
+        <v>434001106525</v>
+      </c>
+      <c r="E729" s="7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F729" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G729" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="730" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A730" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B730" s="4">
+        <v>65</v>
+      </c>
+      <c r="C730" s="5">
+        <v>14671.94</v>
+      </c>
+      <c r="D730" s="6">
+        <v>433732421779</v>
+      </c>
+      <c r="E730" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F730" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G730" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="731" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A731" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B731" s="4">
+        <v>32</v>
+      </c>
+      <c r="C731" s="5">
+        <v>14721.94</v>
+      </c>
+      <c r="D731" s="6">
+        <v>433333360119</v>
+      </c>
+      <c r="E731" s="7" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F731" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G731" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="732" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A732" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B732" s="4">
+        <v>130</v>
+      </c>
+      <c r="C732" s="5">
+        <v>14798.94</v>
+      </c>
+      <c r="D732" s="6">
+        <v>433329232099</v>
+      </c>
+      <c r="E732" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F732" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G732" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="733" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A733" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B733" s="4">
+        <v>29.75</v>
+      </c>
+      <c r="C733" s="5">
+        <v>14926.28</v>
+      </c>
+      <c r="D733" s="6">
+        <v>433306887568</v>
+      </c>
+      <c r="E733" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F733" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G733" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="734" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A734" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B734" s="4">
+        <v>147</v>
+      </c>
+      <c r="C734" s="5">
+        <v>14919.28</v>
+      </c>
+      <c r="D734" s="6">
+        <v>433232586093</v>
+      </c>
+      <c r="E734" s="7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F734" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G734" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="735" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A735" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B735" s="4">
+        <v>70</v>
+      </c>
+      <c r="C735" s="5">
+        <v>15313.86</v>
+      </c>
+      <c r="D735" s="6">
+        <v>432824358080</v>
+      </c>
+      <c r="E735" s="7" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F735" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G735" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="736" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A736" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B736" s="4">
+        <v>480.9</v>
+      </c>
+      <c r="C736" s="5">
+        <v>14657.86</v>
+      </c>
+      <c r="D736" s="6">
+        <v>432592331178</v>
+      </c>
+      <c r="E736" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F736" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G736" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="737" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A737" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B737" s="4">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="C737" s="5">
+        <v>15156.76</v>
+      </c>
+      <c r="D737" s="6">
+        <v>469093966926</v>
+      </c>
+      <c r="E737" s="7" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F737" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G737" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="738" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A738" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B738" s="4">
+        <v>40</v>
+      </c>
+      <c r="C738" s="5">
+        <v>15221.05</v>
+      </c>
+      <c r="D738" s="6">
+        <v>432336233460</v>
+      </c>
+      <c r="E738" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F738" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G738" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="739" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A739" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B739" s="4">
+        <v>120</v>
+      </c>
+      <c r="C739" s="5">
+        <v>15291.05</v>
+      </c>
+      <c r="D739" s="6">
+        <v>432063641912</v>
+      </c>
+      <c r="E739" s="7" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F739" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G739" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="740" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A740" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B740" s="4">
+        <v>8</v>
+      </c>
+      <c r="C740" s="5">
+        <v>15445.05</v>
+      </c>
+      <c r="D740" s="6">
+        <v>468623332583</v>
+      </c>
+      <c r="E740" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F740" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G740" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="741" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A741" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B741" s="4">
+        <v>40</v>
+      </c>
+      <c r="C741" s="5">
+        <v>15473.05</v>
+      </c>
+      <c r="D741" s="6">
+        <v>431999120100</v>
+      </c>
+      <c r="E741" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F741" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G741" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="742" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A742" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B742" s="4">
+        <v>20</v>
+      </c>
+      <c r="C742" s="5">
+        <v>15543.05</v>
+      </c>
+      <c r="D742" s="6">
+        <v>431798587461</v>
+      </c>
+      <c r="E742" s="7" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F742" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G742" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="743" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A743" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B743" s="4">
+        <v>10</v>
+      </c>
+      <c r="C743" s="5">
+        <v>15563.05</v>
+      </c>
+      <c r="D743" s="6">
+        <v>431629062707</v>
+      </c>
+      <c r="E743" s="7" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F743" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G743" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="744" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A744" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B744" s="4">
+        <v>10</v>
+      </c>
+      <c r="C744" s="5">
+        <v>18587.05</v>
+      </c>
+      <c r="D744" s="6">
+        <v>431516489847</v>
+      </c>
+      <c r="E744" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F744" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G744" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="745" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A745" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B745" s="4">
+        <v>83.75</v>
+      </c>
+      <c r="C745" s="5">
+        <v>15213.05</v>
+      </c>
+      <c r="D745" s="6">
+        <v>431468291533</v>
+      </c>
+      <c r="E745" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F745" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G745" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="746" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A746" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B746" s="4">
+        <v>10</v>
+      </c>
+      <c r="C746" s="5">
+        <v>15419.8</v>
+      </c>
+      <c r="D746" s="6">
+        <v>431391974662</v>
+      </c>
+      <c r="E746" s="7" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F746" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G746" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="747" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A747" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B747" s="4">
+        <v>15</v>
+      </c>
+      <c r="C747" s="5">
+        <v>15474.8</v>
+      </c>
+      <c r="D747" s="6">
+        <v>431224708899</v>
+      </c>
+      <c r="E747" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F747" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G747" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="748" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A748" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B748" s="4">
+        <v>350</v>
+      </c>
+      <c r="C748" s="5">
+        <v>15489.8</v>
+      </c>
+      <c r="D748" s="6">
+        <v>431233157396</v>
+      </c>
+      <c r="E748" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="F748" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G748" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="749" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A749" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B749" s="4">
+        <v>15</v>
+      </c>
+      <c r="C749" s="5">
+        <v>19199.8</v>
+      </c>
+      <c r="D749" s="6">
+        <v>431052196448</v>
+      </c>
+      <c r="E749" s="7" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F749" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G749" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="750" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A750" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B750" s="4">
+        <v>1500</v>
+      </c>
+      <c r="C750" s="5">
+        <v>17368.990000000002</v>
+      </c>
+      <c r="D750" s="6">
+        <v>428567290288</v>
+      </c>
+      <c r="E750" s="7" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F750" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G750" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="751" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A751" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B751" s="4">
+        <v>9</v>
+      </c>
+      <c r="C751" s="5">
+        <v>15446.49</v>
+      </c>
+      <c r="D751" s="6">
+        <v>427694580608</v>
+      </c>
+      <c r="E751" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F751" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G751" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="752" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A752" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B752" s="4">
+        <v>20</v>
+      </c>
+      <c r="C752" s="5">
+        <v>15455.49</v>
+      </c>
+      <c r="D752" s="6">
+        <v>427533579238</v>
+      </c>
+      <c r="E752" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F752" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G752" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="753" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A753" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B753" s="4">
+        <v>10</v>
+      </c>
+      <c r="C753" s="5">
+        <v>14207.39</v>
+      </c>
+      <c r="D753" s="6">
+        <v>463503700812</v>
+      </c>
+      <c r="E753" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F753" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G753" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="754" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A754" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B754" s="4">
+        <v>20</v>
+      </c>
+      <c r="C754" s="5">
+        <v>14262.39</v>
+      </c>
+      <c r="D754" s="6">
+        <v>426785884938</v>
+      </c>
+      <c r="E754" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F754" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G754" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="755" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A755" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B755" s="4">
+        <v>45</v>
+      </c>
+      <c r="C755" s="5">
+        <v>14282.39</v>
+      </c>
+      <c r="D755" s="6">
+        <v>426733434338</v>
+      </c>
+      <c r="E755" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F755" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G755" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="756" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A756" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B756" s="4">
+        <v>70</v>
+      </c>
+      <c r="C756" s="5">
+        <v>12827.39</v>
+      </c>
+      <c r="D756" s="6">
+        <v>426695098291</v>
+      </c>
+      <c r="E756" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F756" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G756" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="757" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A757" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B757" s="4">
+        <v>22</v>
+      </c>
+      <c r="C757" s="5">
+        <v>12952.39</v>
+      </c>
+      <c r="D757" s="6">
+        <v>426061519046</v>
+      </c>
+      <c r="E757" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F757" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G757" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="758" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A758" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B758" s="4">
+        <v>22</v>
+      </c>
+      <c r="C758" s="5">
+        <v>12974.39</v>
+      </c>
+      <c r="D758" s="6">
+        <v>425912718767</v>
+      </c>
+      <c r="E758" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F758" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G758" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="759" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A759" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B759" s="4">
+        <v>65</v>
+      </c>
+      <c r="C759" s="5">
+        <v>13032.39</v>
+      </c>
+      <c r="D759" s="6">
+        <v>425709850517</v>
+      </c>
+      <c r="E759" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F759" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G759" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="760" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A760" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B760" s="4">
+        <v>312</v>
+      </c>
+      <c r="C760" s="5">
+        <v>12925.39</v>
+      </c>
+      <c r="D760" s="6">
+        <v>425645589558</v>
+      </c>
+      <c r="E760" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F760" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G760" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="761" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A761" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B761" s="4">
+        <v>40</v>
+      </c>
+      <c r="C761" s="5">
+        <v>13237.39</v>
+      </c>
+      <c r="D761" s="6">
+        <v>425660199644</v>
+      </c>
+      <c r="E761" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F761" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G761" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="762" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A762" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B762" s="4">
+        <v>20</v>
+      </c>
+      <c r="C762" s="5">
+        <v>13277.39</v>
+      </c>
+      <c r="D762" s="6">
+        <v>462160969985</v>
+      </c>
+      <c r="E762" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F762" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G762" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="763" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A763" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B763" s="4">
+        <v>10</v>
+      </c>
+      <c r="C763" s="5">
+        <v>15225.39</v>
+      </c>
+      <c r="D763" s="6">
+        <v>425463325072</v>
+      </c>
+      <c r="E763" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F763" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G763" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="764" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A764" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B764" s="4">
+        <v>800</v>
+      </c>
+      <c r="C764" s="5">
+        <v>14255.39</v>
+      </c>
+      <c r="D764" s="6">
+        <v>425289584586</v>
+      </c>
+      <c r="E764" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="F764" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G764" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="765" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A765" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B765" s="4">
+        <v>179</v>
+      </c>
+      <c r="C765" s="5">
+        <v>9781.39</v>
+      </c>
+      <c r="D765" s="6">
+        <v>425146062318</v>
+      </c>
+      <c r="E765" s="7" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F765" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G765" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="766" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A766" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B766" s="4">
+        <v>60</v>
+      </c>
+      <c r="C766" s="5">
+        <v>9942.39</v>
+      </c>
+      <c r="D766" s="6">
+        <v>425110967737</v>
+      </c>
+      <c r="E766" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F766" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G766" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="767" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A767" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B767" s="4">
+        <v>70</v>
+      </c>
+      <c r="C767" s="5">
+        <v>11951.37</v>
+      </c>
+      <c r="D767" s="6">
+        <v>460740357681</v>
+      </c>
+      <c r="E767" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F767" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G767" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="768" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A768" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B768" s="4">
+        <v>231</v>
+      </c>
+      <c r="C768" s="5">
+        <v>12021.37</v>
+      </c>
+      <c r="D768" s="6">
+        <v>424026050979</v>
+      </c>
+      <c r="E768" s="7" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F768" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G768" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="769" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A769" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B769" s="4">
+        <v>500</v>
+      </c>
+      <c r="C769" s="5">
+        <v>12252.37</v>
+      </c>
+      <c r="D769" s="6">
+        <v>423907144048</v>
+      </c>
+      <c r="E769" s="7" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F769" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G769" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="770" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A770" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B770" s="4">
+        <v>60</v>
+      </c>
+      <c r="C770" s="5">
+        <v>12967.37</v>
+      </c>
+      <c r="D770" s="6">
+        <v>460348226551</v>
+      </c>
+      <c r="E770" s="7" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F770" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G770" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="771" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A771" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B771" s="4">
+        <v>70</v>
+      </c>
+      <c r="C771" s="5">
+        <v>13022.37</v>
+      </c>
+      <c r="D771" s="6">
+        <v>423697179107</v>
+      </c>
+      <c r="E771" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F771" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G771" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="772" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A772" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B772" s="4">
+        <v>140</v>
+      </c>
+      <c r="C772" s="5">
+        <v>13013.04</v>
+      </c>
+      <c r="D772" s="6">
+        <v>423695045000</v>
+      </c>
+      <c r="E772" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F772" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G772" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="773" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A773" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B773" s="4">
+        <v>50</v>
+      </c>
+      <c r="C773" s="5">
+        <v>13153.04</v>
+      </c>
+      <c r="D773" s="6">
+        <v>460224433683</v>
+      </c>
+      <c r="E773" s="7" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F773" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G773" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="774" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A774" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B774" s="4">
+        <v>100</v>
+      </c>
+      <c r="C774" s="5">
+        <v>13203.04</v>
+      </c>
+      <c r="D774" s="6">
+        <v>423562875714</v>
+      </c>
+      <c r="E774" s="7" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F774" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G774" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="775" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A775" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B775" s="4">
+        <v>20</v>
+      </c>
+      <c r="C775" s="5">
+        <v>13303.04</v>
+      </c>
+      <c r="D775" s="6">
+        <v>423495435346</v>
+      </c>
+      <c r="E775" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F775" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G775" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="776" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A776" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B776" s="4">
+        <v>96</v>
+      </c>
+      <c r="C776" s="5">
+        <v>13275.04</v>
+      </c>
+      <c r="D776" s="6">
+        <v>423355441934</v>
+      </c>
+      <c r="E776" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F776" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G776" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="777" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A777" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B777" s="4">
+        <v>22</v>
+      </c>
+      <c r="C777" s="5">
+        <v>12886.04</v>
+      </c>
+      <c r="D777" s="6">
+        <v>423331479702</v>
+      </c>
+      <c r="E777" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F777" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G777" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="778" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A778" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B778" s="4">
+        <v>22</v>
+      </c>
+      <c r="C778" s="5">
+        <v>12908.04</v>
+      </c>
+      <c r="D778" s="6">
+        <v>423205916378</v>
+      </c>
+      <c r="E778" s="7" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F778" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G778" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="779" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A779" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B779" s="4">
+        <v>65</v>
+      </c>
+      <c r="C779" s="5">
+        <v>12975.04</v>
+      </c>
+      <c r="D779" s="6">
+        <v>423138359062</v>
+      </c>
+      <c r="E779" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F779" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G779" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="780" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A780" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B780" s="4">
+        <v>20</v>
+      </c>
+      <c r="C780" s="5">
+        <v>13040.04</v>
+      </c>
+      <c r="D780" s="6">
+        <v>423015805011</v>
+      </c>
+      <c r="E780" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="F780" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G780" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="781" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A781" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B781" s="4">
+        <v>20</v>
+      </c>
+      <c r="C781" s="5">
+        <v>13060.04</v>
+      </c>
+      <c r="D781" s="6">
+        <v>422966408462</v>
+      </c>
+      <c r="E781" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F781" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G781" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="782" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A782" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B782" s="4">
+        <v>10</v>
+      </c>
+      <c r="C782" s="5">
+        <v>2204.96</v>
+      </c>
+      <c r="D782" s="6">
+        <v>404096839443</v>
+      </c>
+      <c r="E782" s="7" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F782" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G782" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="783" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A783" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B783" s="4">
+        <v>25</v>
+      </c>
+      <c r="C783" s="5">
+        <v>2224.96</v>
+      </c>
+      <c r="D783" s="6">
+        <v>440508831268</v>
+      </c>
+      <c r="E783" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F783" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G783" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="784" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A784" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B784" s="4">
+        <v>30</v>
+      </c>
+      <c r="C784" s="5">
+        <v>2008.96</v>
+      </c>
+      <c r="D784" s="6">
+        <v>440291567464</v>
+      </c>
+      <c r="E784" s="7" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F784" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G784" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="785" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A785" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B785" s="4">
+        <v>20</v>
+      </c>
+      <c r="C785" s="5">
+        <v>2038.96</v>
+      </c>
+      <c r="D785" s="6">
+        <v>440246736137</v>
+      </c>
+      <c r="E785" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F785" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G785" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="786" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A786" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B786" s="4">
+        <v>20</v>
+      </c>
+      <c r="C786" s="5">
+        <v>2098.96</v>
+      </c>
+      <c r="D786" s="6">
+        <v>403612040330</v>
+      </c>
+      <c r="E786" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F786" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G786" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="787" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A787" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B787" s="4">
+        <v>25</v>
+      </c>
+      <c r="C787" s="5">
+        <v>2118.96</v>
+      </c>
+      <c r="D787" s="6">
+        <v>403611953580</v>
+      </c>
+      <c r="E787" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F787" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G787" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="788" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A788" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B788" s="4">
+        <v>5</v>
+      </c>
+      <c r="C788" s="5">
+        <v>2143.96</v>
+      </c>
+      <c r="D788" s="6">
+        <v>440160215924</v>
+      </c>
+      <c r="E788" s="7" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F788" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G788" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="789" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A789" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B789" s="4">
+        <v>10</v>
+      </c>
+      <c r="C789" s="5">
+        <v>2148.96</v>
+      </c>
+      <c r="D789" s="6">
+        <v>403591008558</v>
+      </c>
+      <c r="E789" s="7" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F789" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G789" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="790" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A790" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B790" s="4">
+        <v>22</v>
+      </c>
+      <c r="C790" s="5">
+        <v>2184.96</v>
+      </c>
+      <c r="D790" s="6">
+        <v>403500992249</v>
+      </c>
+      <c r="E790" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F790" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G790" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="791" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A791" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B791" s="4">
+        <v>10</v>
+      </c>
+      <c r="C791" s="5">
+        <v>2206.96</v>
+      </c>
+      <c r="D791" s="6">
+        <v>403585856738</v>
+      </c>
+      <c r="E791" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="F791" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G791" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="792" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A792" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B792" s="4">
+        <v>70</v>
+      </c>
+      <c r="C792" s="5">
+        <v>2216.96</v>
+      </c>
+      <c r="D792" s="6">
+        <v>403585118355</v>
+      </c>
+      <c r="E792" s="7" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F792" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G792" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="793" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A793" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B793" s="4">
+        <v>100</v>
+      </c>
+      <c r="C793" s="5">
+        <v>2286.96</v>
+      </c>
+      <c r="D793" s="6">
+        <v>440117780984</v>
+      </c>
+      <c r="E793" s="7" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F793" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G793" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="794" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A794" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B794" s="4">
+        <v>25</v>
+      </c>
+      <c r="C794" s="5">
+        <v>2386.96</v>
+      </c>
+      <c r="D794" s="6">
+        <v>403574710829</v>
+      </c>
+      <c r="E794" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F794" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G794" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="795" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A795" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B795" s="4">
+        <v>30</v>
+      </c>
+      <c r="C795" s="5">
+        <v>2411.96</v>
+      </c>
+      <c r="D795" s="6">
+        <v>403467195025</v>
+      </c>
+      <c r="E795" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F795" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G795" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="796" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A796" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B796" s="4">
+        <v>25</v>
+      </c>
+      <c r="C796" s="5">
+        <v>2481.96</v>
+      </c>
+      <c r="D796" s="6">
+        <v>440065318621</v>
+      </c>
+      <c r="E796" s="7" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F796" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G796" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="797" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A797" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B797" s="4">
+        <v>25</v>
+      </c>
+      <c r="C797" s="5">
+        <v>2506.96</v>
+      </c>
+      <c r="D797" s="6">
+        <v>403394381740</v>
+      </c>
+      <c r="E797" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F797" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G797" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="798" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A798" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B798" s="4">
+        <v>20</v>
+      </c>
+      <c r="C798" s="5">
+        <v>2531.96</v>
+      </c>
+      <c r="D798" s="6">
+        <v>403275179245</v>
+      </c>
+      <c r="E798" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F798" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G798" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="799" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A799" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B799" s="4">
+        <v>17</v>
+      </c>
+      <c r="C799" s="5">
+        <v>2547.96</v>
+      </c>
+      <c r="D799" s="6">
+        <v>402823643933</v>
+      </c>
+      <c r="E799" s="7" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F799" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G799" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="800" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A800" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B800" s="4">
+        <v>60</v>
+      </c>
+      <c r="C800" s="5">
+        <v>2549.96</v>
+      </c>
+      <c r="D800" s="6">
+        <v>401997186893</v>
+      </c>
+      <c r="E800" s="7" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F800" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G800" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="801" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A801" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B801" s="4">
+        <v>12</v>
+      </c>
+      <c r="C801" s="5">
+        <v>2737.96</v>
+      </c>
+      <c r="D801" s="6">
+        <v>401562414976</v>
+      </c>
+      <c r="E801" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F801" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G801" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="802" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A802" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B802" s="4">
+        <v>70</v>
+      </c>
+      <c r="C802" s="5">
+        <v>2749.96</v>
+      </c>
+      <c r="D802" s="6">
+        <v>401535516932</v>
+      </c>
+      <c r="E802" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F802" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G802" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="803" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A803" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B803" s="4">
+        <v>200</v>
+      </c>
+      <c r="C803" s="5">
+        <v>5260.96</v>
+      </c>
+      <c r="D803" s="6">
+        <v>400926996504</v>
+      </c>
+      <c r="E803" s="7" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F803" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G803" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="804" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A804" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B804" s="4">
+        <v>17</v>
+      </c>
+      <c r="C804" s="5">
+        <v>1321.96</v>
+      </c>
+      <c r="D804" s="6">
+        <v>400445517634</v>
+      </c>
+      <c r="E804" s="7" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F804" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G804" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="805" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A805" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B805" s="4">
+        <v>50</v>
+      </c>
+      <c r="C805" s="5">
+        <v>1138.96</v>
+      </c>
+      <c r="D805" s="6">
+        <v>436830288556</v>
+      </c>
+      <c r="E805" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F805" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G805" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="806" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A806" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B806" s="4">
+        <v>100</v>
+      </c>
+      <c r="C806" s="5">
+        <v>1188.96</v>
+      </c>
+      <c r="D806" s="6">
+        <v>400246676172</v>
+      </c>
+      <c r="E806" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F806" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G806" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="807" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A807" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B807" s="4">
+        <v>40</v>
+      </c>
+      <c r="C807" s="5">
+        <v>1238.96</v>
+      </c>
+      <c r="D807" s="6">
+        <v>400261877401</v>
+      </c>
+      <c r="E807" s="7" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F807" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G807" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="808" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A808" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B808" s="4">
+        <v>80</v>
+      </c>
+      <c r="C808" s="5">
+        <v>4649.46</v>
+      </c>
+      <c r="D808" s="6">
+        <v>335273958025</v>
+      </c>
+      <c r="E808" s="7" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F808" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G808" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="809" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A809" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B809" s="4">
+        <v>27</v>
+      </c>
+      <c r="C809" s="5">
+        <v>1119.46</v>
+      </c>
+      <c r="D809" s="6">
+        <v>334882565406</v>
+      </c>
+      <c r="E809" s="7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F809" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G809" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="810" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A810" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B810" s="4">
+        <v>30</v>
+      </c>
+      <c r="C810" s="5">
+        <v>1096.46</v>
+      </c>
+      <c r="D810" s="6">
+        <v>371360103950</v>
+      </c>
+      <c r="E810" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F810" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G810" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="811" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A811" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B811" s="4">
+        <v>12</v>
+      </c>
+      <c r="C811" s="5">
+        <v>1126.46</v>
+      </c>
+      <c r="D811" s="6">
+        <v>334754552799</v>
+      </c>
+      <c r="E811" s="7" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F811" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G811" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="812" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A812" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B812" s="4">
+        <v>10</v>
+      </c>
+      <c r="C812" s="5">
+        <v>1254.46</v>
+      </c>
+      <c r="D812" s="6">
+        <v>371058646917</v>
+      </c>
+      <c r="E812" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F812" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G812" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="813" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A813" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B813" s="4">
+        <v>60</v>
+      </c>
+      <c r="C813" s="5">
+        <v>1475.46</v>
+      </c>
+      <c r="D813" s="6">
+        <v>334440808550</v>
+      </c>
+      <c r="E813" s="7" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F813" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G813" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="814" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A814" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B814" s="4">
+        <v>10</v>
+      </c>
+      <c r="C814" s="5">
+        <v>1595.46</v>
+      </c>
+      <c r="D814" s="6">
+        <v>334287821437</v>
+      </c>
+      <c r="E814" s="7" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F814" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G814" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="815" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A815" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B815" s="4">
+        <v>3200</v>
+      </c>
+      <c r="C815" s="5">
+        <v>4363.46</v>
+      </c>
+      <c r="D815" s="6">
+        <v>334161871242</v>
+      </c>
+      <c r="E815" s="7" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F815" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G815" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="816" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A816" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B816" s="4">
+        <v>7</v>
+      </c>
+      <c r="C816" s="5">
+        <v>1598.46</v>
+      </c>
+      <c r="D816" s="6">
+        <v>370686618312</v>
+      </c>
+      <c r="E816" s="7" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F816" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G816" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="817" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A817" s="3" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B817" s="4">
+        <v>10</v>
+      </c>
+      <c r="C817" s="5">
+        <v>1605.46</v>
+      </c>
+      <c r="D817" s="6">
+        <v>333901779332</v>
+      </c>
+      <c r="E817" s="7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F817" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G817" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="818" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A818" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B818" s="4">
+        <v>13</v>
+      </c>
+      <c r="C818" s="5">
+        <v>1495.46</v>
+      </c>
+      <c r="D818" s="6">
+        <v>333052718476</v>
+      </c>
+      <c r="E818" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F818" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G818" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="819" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A819" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B819" s="4">
+        <v>70</v>
+      </c>
+      <c r="C819" s="5">
+        <v>1518.46</v>
+      </c>
+      <c r="D819" s="6">
+        <v>333068134052</v>
+      </c>
+      <c r="E819" s="7" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F819" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G819" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="820" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A820" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B820" s="4">
+        <v>10</v>
+      </c>
+      <c r="C820" s="5">
+        <v>1588.46</v>
+      </c>
+      <c r="D820" s="6">
+        <v>332901578631</v>
+      </c>
+      <c r="E820" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F820" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G820" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="821" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A821" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B821" s="4">
+        <v>100</v>
+      </c>
+      <c r="C821" s="5">
+        <v>1548.46</v>
+      </c>
+      <c r="D821" s="6">
+        <v>332940482146</v>
+      </c>
+      <c r="E821" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="F821" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G821" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="822" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A822" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B822" s="4">
+        <v>80</v>
+      </c>
+      <c r="C822" s="5">
+        <v>1668.46</v>
+      </c>
+      <c r="D822" s="6">
+        <v>332953989490</v>
+      </c>
+      <c r="E822" s="7" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F822" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G822" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="823" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A823" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B823" s="4">
+        <v>60</v>
+      </c>
+      <c r="C823" s="5">
+        <v>1748.46</v>
+      </c>
+      <c r="D823" s="6">
+        <v>332950238210</v>
+      </c>
+      <c r="E823" s="7" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F823" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G823" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="824" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A824" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B824" s="4">
+        <v>5</v>
+      </c>
+      <c r="C824" s="5">
+        <v>1858.46</v>
+      </c>
+      <c r="D824" s="6">
+        <v>332596068569</v>
+      </c>
+      <c r="E824" s="7" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F824" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G824" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="825" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A825" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B825" s="4">
+        <v>10</v>
+      </c>
+      <c r="C825" s="5">
+        <v>1873.46</v>
+      </c>
+      <c r="D825" s="6">
+        <v>332443382989</v>
+      </c>
+      <c r="E825" s="7" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F825" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G825" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="826" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A826" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B826" s="4">
+        <v>150</v>
+      </c>
+      <c r="C826" s="5">
+        <v>1853.46</v>
+      </c>
+      <c r="D826" s="6">
+        <v>332197092029</v>
+      </c>
+      <c r="E826" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F826" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G826" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="827" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A827" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B827" s="4">
+        <v>150</v>
+      </c>
+      <c r="C827" s="5">
+        <v>1953.46</v>
+      </c>
+      <c r="D827" s="6">
+        <v>368792655995</v>
+      </c>
+      <c r="E827" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F827" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G827" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="828" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A828" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B828" s="4">
+        <v>200</v>
+      </c>
+      <c r="C828" s="5">
+        <v>1973.46</v>
+      </c>
+      <c r="D828" s="6">
+        <v>332050630905</v>
+      </c>
+      <c r="E828" s="7" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F828" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G828" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="829" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A829" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B829" s="4">
+        <v>49</v>
+      </c>
+      <c r="C829" s="5">
+        <v>2454.46</v>
+      </c>
+      <c r="D829" s="6">
+        <v>331745183972</v>
+      </c>
+      <c r="E829" s="7" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F829" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G829" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="830" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A830" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B830" s="4">
+        <v>18</v>
+      </c>
+      <c r="C830" s="5">
+        <v>2523.46</v>
+      </c>
+      <c r="D830" s="6">
+        <v>331733975971</v>
+      </c>
+      <c r="E830" s="7" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F830" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G830" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="831" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A831" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B831" s="4">
+        <v>47</v>
+      </c>
+      <c r="C831" s="5">
+        <v>2437.46</v>
+      </c>
+      <c r="D831" s="6">
+        <v>331774278736</v>
+      </c>
+      <c r="E831" s="7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F831" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G831" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="832" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A832" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B832" s="4">
+        <v>20</v>
+      </c>
+      <c r="C832" s="5">
+        <v>2484.46</v>
+      </c>
+      <c r="D832" s="6">
+        <v>331797208496</v>
+      </c>
+      <c r="E832" s="7" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F832" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G832" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="833" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A833" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B833" s="4">
+        <v>87</v>
+      </c>
+      <c r="C833" s="5">
+        <v>2504.46</v>
+      </c>
+      <c r="D833" s="6">
+        <v>331642070238</v>
+      </c>
+      <c r="E833" s="7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F833" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G833" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="834" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A834" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B834" s="4">
+        <v>5</v>
+      </c>
+      <c r="C834" s="5">
+        <v>5933.46</v>
+      </c>
+      <c r="D834" s="6">
+        <v>331458853287</v>
+      </c>
+      <c r="E834" s="7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F834" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G834" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="835" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A835" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B835" s="4">
+        <v>10</v>
+      </c>
+      <c r="C835" s="5">
+        <v>5948.46</v>
+      </c>
+      <c r="D835" s="6">
+        <v>331310420613</v>
+      </c>
+      <c r="E835" s="7" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F835" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G835" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="836" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A836" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B836" s="4">
+        <v>2770</v>
+      </c>
+      <c r="C836" s="5">
+        <v>5963.46</v>
+      </c>
+      <c r="D836" s="6">
+        <v>331274761601</v>
+      </c>
+      <c r="E836" s="7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F836" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G836" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="837" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A837" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B837" s="4">
+        <v>176</v>
+      </c>
+      <c r="C837" s="5">
+        <v>8733.4599999999991</v>
+      </c>
+      <c r="D837" s="6">
+        <v>331173924507</v>
+      </c>
+      <c r="E837" s="7" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F837" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G837" s="7" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="838" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A838" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B838" s="9">
+        <v>540</v>
+      </c>
+      <c r="D838" s="10">
+        <v>162360611494</v>
+      </c>
+      <c r="F838" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G838" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="839" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A839" s="8" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B839" s="9">
+        <v>6</v>
+      </c>
+      <c r="D839" s="10">
+        <v>549209304901</v>
+      </c>
+      <c r="F839" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G839" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="840" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A840" s="8" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B840" s="9">
+        <v>240</v>
+      </c>
+      <c r="D840" s="10">
+        <v>512316990685</v>
+      </c>
+      <c r="F840" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G840" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="841" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A841" s="8" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B841" s="9">
+        <v>100</v>
+      </c>
+      <c r="D841" s="10">
+        <v>510643114404</v>
+      </c>
+      <c r="F841" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G841" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="842" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A842" s="8" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B842" s="9">
+        <v>66</v>
+      </c>
+      <c r="D842" s="10">
+        <v>509895954242</v>
+      </c>
+      <c r="F842" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G842" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="843" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A843" s="8" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B843" s="9">
+        <v>30</v>
+      </c>
+      <c r="D843" s="10">
+        <v>509717934785</v>
+      </c>
+      <c r="F843" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G843" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="844" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A844" s="8" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B844" s="9">
+        <v>1150</v>
+      </c>
+      <c r="D844" s="10">
+        <v>544831141451</v>
+      </c>
+      <c r="F844" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G844" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="845" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A845" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B845" s="9">
+        <v>140</v>
+      </c>
+      <c r="D845" s="10">
+        <v>506771811042</v>
+      </c>
+      <c r="F845" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G845" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="846" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A846" s="8" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B846" s="9">
+        <v>30</v>
+      </c>
+      <c r="D846" s="10">
+        <v>506771778176</v>
+      </c>
+      <c r="F846" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G846" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="847" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A847" s="8" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B847" s="9">
+        <v>30</v>
+      </c>
+      <c r="D847" s="10">
+        <v>506771756678</v>
+      </c>
+      <c r="F847" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G847" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="848" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A848" s="8" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B848" s="9">
+        <v>20</v>
+      </c>
+      <c r="D848" s="10">
+        <v>100381880706</v>
+      </c>
+      <c r="F848" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G848" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="849" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A849" s="8" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B849" s="9">
+        <v>30</v>
+      </c>
+      <c r="D849" s="10">
+        <v>505052848954</v>
+      </c>
+      <c r="F849" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G849" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="850" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A850" s="8" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B850" s="9">
+        <v>20</v>
+      </c>
+      <c r="D850" s="10">
+        <v>503484642527</v>
+      </c>
+      <c r="F850" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G850" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="851" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A851" s="8" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B851" s="9">
+        <v>20</v>
+      </c>
+      <c r="D851" s="10">
+        <v>503403439470</v>
+      </c>
+      <c r="F851" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G851" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="852" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A852" s="8" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B852" s="9">
+        <v>500</v>
+      </c>
+      <c r="D852" s="10">
+        <v>654343762920</v>
+      </c>
+      <c r="F852" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G852" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="853" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A853" s="8" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B853" s="9">
+        <v>206.25</v>
+      </c>
+      <c r="D853" s="10">
+        <v>502314475367</v>
+      </c>
+      <c r="F853" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G853" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="854" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A854" s="8" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B854" s="9">
+        <v>148</v>
+      </c>
+      <c r="D854" s="10">
+        <v>436196809547</v>
+      </c>
+      <c r="F854" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G854" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="855" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A855" s="8" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B855" s="9">
+        <v>20</v>
+      </c>
+      <c r="D855" s="10">
+        <v>436196500081</v>
+      </c>
+      <c r="F855" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G855" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="856" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A856" s="8" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B856" s="9">
+        <v>7</v>
+      </c>
+      <c r="D856" s="10">
+        <v>434399342919</v>
+      </c>
+      <c r="F856" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G856" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="857" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A857" s="8" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B857" s="9">
+        <v>50</v>
+      </c>
+      <c r="D857" s="10">
+        <v>470239288626</v>
+      </c>
+      <c r="F857" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G857" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="858" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A858" s="8" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B858" s="9">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="D858" s="10">
+        <v>469965884741</v>
+      </c>
+      <c r="F858" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G858" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="859" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A859" s="8" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B859" s="9">
+        <v>3500</v>
+      </c>
+      <c r="D859" s="10">
+        <v>863822523607</v>
+      </c>
+      <c r="F859" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G859" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="860" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A860" s="8" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B860" s="9">
+        <v>34</v>
+      </c>
+      <c r="D860" s="10">
+        <v>428622605005</v>
+      </c>
+      <c r="F860" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G860" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="861" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A861" s="8" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B861" s="9">
+        <v>3500</v>
+      </c>
+      <c r="D861" s="10">
+        <v>427889762227</v>
+      </c>
+      <c r="F861" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G861" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="862" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A862" s="8" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B862" s="9">
+        <v>3000</v>
+      </c>
+      <c r="D862" s="10">
+        <v>427194705462</v>
+      </c>
+      <c r="F862" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G862" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="863" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A863" s="8" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B863" s="9">
+        <v>1500</v>
+      </c>
+      <c r="D863" s="10">
+        <v>426674914878</v>
+      </c>
+      <c r="F863" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G863" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="864" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A864" s="8" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B864" s="9">
+        <v>172</v>
+      </c>
+      <c r="D864" s="10">
+        <v>425651991122</v>
+      </c>
+      <c r="F864" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G864" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="865" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A865" s="8" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B865" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D865" s="10">
+        <v>425268699120</v>
+      </c>
+      <c r="F865" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G865" s="11" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="866" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A866" s="12" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B866" s="13">
+        <v>75</v>
+      </c>
+      <c r="D866" s="14">
+        <v>513790184764</v>
+      </c>
+      <c r="F866" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G866" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="867" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A867" s="12" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B867" s="13">
+        <v>540.9</v>
+      </c>
+      <c r="D867" s="14">
+        <v>513568982781</v>
+      </c>
+      <c r="F867" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G867" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="868" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A868" s="12" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B868" s="13">
+        <v>40</v>
+      </c>
+      <c r="D868" s="14">
+        <v>513568443202</v>
+      </c>
+      <c r="F868" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G868" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="869" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A869" s="12" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B869" s="13">
+        <v>100</v>
+      </c>
+      <c r="D869" s="14">
+        <v>512805384242</v>
+      </c>
+      <c r="F869" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G869" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="870" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A870" s="12" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B870" s="13">
+        <v>50</v>
+      </c>
+      <c r="D870" s="14">
+        <v>549351364210</v>
+      </c>
+      <c r="F870" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G870" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="871" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A871" s="12" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B871" s="13">
+        <v>105</v>
+      </c>
+      <c r="D871" s="14">
+        <v>512638690911</v>
+      </c>
+      <c r="F871" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G871" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="872" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A872" s="12" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B872" s="13">
+        <v>45</v>
+      </c>
+      <c r="D872" s="14">
+        <v>512619522924</v>
+      </c>
+      <c r="F872" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G872" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="873" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A873" s="12" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B873" s="13">
+        <v>93</v>
+      </c>
+      <c r="D873" s="14">
+        <v>549155830074</v>
+      </c>
+      <c r="F873" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G873" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="874" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A874" s="12" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B874" s="13">
+        <v>10</v>
+      </c>
+      <c r="D874" s="14">
+        <v>512192533605</v>
+      </c>
+      <c r="F874" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G874" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="875" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A875" s="12" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B875" s="13">
+        <v>230</v>
+      </c>
+      <c r="D875" s="14">
+        <v>511546376094</v>
+      </c>
+      <c r="F875" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G875" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="876" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A876" s="12" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B876" s="13">
+        <v>200.88</v>
+      </c>
+      <c r="D876" s="14">
+        <v>511540965902</v>
+      </c>
+      <c r="F876" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G876" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="877" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A877" s="12" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B877" s="13">
+        <v>65</v>
+      </c>
+      <c r="D877" s="14">
+        <v>510287696316</v>
+      </c>
+      <c r="F877" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G877" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="878" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A878" s="12" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B878" s="13">
+        <v>10</v>
+      </c>
+      <c r="D878" s="14">
+        <v>509890451454</v>
+      </c>
+      <c r="F878" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G878" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="879" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A879" s="12" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B879" s="13">
+        <v>150</v>
+      </c>
+      <c r="D879" s="14">
+        <v>508763205837</v>
+      </c>
+      <c r="F879" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G879" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="880" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A880" s="12" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B880" s="13">
+        <v>85</v>
+      </c>
+      <c r="D880" s="14">
+        <v>508319600606</v>
+      </c>
+      <c r="F880" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G880" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="881" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A881" s="12" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B881" s="13">
+        <v>105</v>
+      </c>
+      <c r="D881" s="14">
+        <v>544824901842</v>
+      </c>
+      <c r="F881" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G881" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="882" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A882" s="12" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B882" s="13">
+        <v>50</v>
+      </c>
+      <c r="D882" s="14">
+        <v>544178374947</v>
+      </c>
+      <c r="F882" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G882" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="883" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A883" s="12" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B883" s="13">
+        <v>60</v>
+      </c>
+      <c r="D883" s="14">
+        <v>507448369107</v>
+      </c>
+      <c r="F883" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G883" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="884" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A884" s="12" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B884" s="13">
+        <v>980</v>
+      </c>
+      <c r="D884" s="14">
+        <v>507237856648</v>
+      </c>
+      <c r="F884" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G884" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="885" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A885" s="12" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B885" s="13">
+        <v>1452</v>
+      </c>
+      <c r="D885" s="14">
+        <v>506732696643</v>
+      </c>
+      <c r="F885" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G885" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="886" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A886" s="12" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B886" s="13">
+        <v>18</v>
+      </c>
+      <c r="D886" s="14">
+        <v>506645536192</v>
+      </c>
+      <c r="F886" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G886" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="887" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A887" s="12" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B887" s="13">
+        <v>28.33</v>
+      </c>
+      <c r="D887" s="14">
+        <v>101059178060</v>
+      </c>
+      <c r="F887" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G887" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="888" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A888" s="12" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B888" s="13">
+        <v>3250</v>
+      </c>
+      <c r="D888" s="14">
+        <v>506539123537</v>
+      </c>
+      <c r="F888" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G888" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="889" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A889" s="12" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B889" s="13">
+        <v>255</v>
+      </c>
+      <c r="D889" s="14">
+        <v>505947119294</v>
+      </c>
+      <c r="F889" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G889" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="890" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A890" s="12" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B890" s="13">
+        <v>48</v>
+      </c>
+      <c r="D890" s="14">
+        <v>505911866474</v>
+      </c>
+      <c r="F890" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G890" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="891" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A891" s="12" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B891" s="13">
+        <v>12</v>
+      </c>
+      <c r="D891" s="14">
+        <v>542161036690</v>
+      </c>
+      <c r="F891" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G891" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="892" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A892" s="12" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B892" s="13">
+        <v>60</v>
+      </c>
+      <c r="D892" s="14">
+        <v>505214963622</v>
+      </c>
+      <c r="F892" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G892" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="893" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A893" s="12" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B893" s="13">
+        <v>15</v>
+      </c>
+      <c r="D893" s="14">
+        <v>541709141275</v>
+      </c>
+      <c r="F893" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G893" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="894" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A894" s="12" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B894" s="13">
+        <v>90</v>
+      </c>
+      <c r="D894" s="14">
+        <v>504489238199</v>
+      </c>
+      <c r="F894" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G894" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="895" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A895" s="12" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B895" s="13">
+        <v>60</v>
+      </c>
+      <c r="D895" s="14">
+        <v>503858947936</v>
+      </c>
+      <c r="F895" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G895" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="896" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A896" s="12" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B896" s="13">
+        <v>175</v>
+      </c>
+      <c r="D896" s="14">
+        <v>503536735392</v>
+      </c>
+      <c r="F896" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G896" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="897" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A897" s="12" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B897" s="13">
+        <v>35</v>
+      </c>
+      <c r="D897" s="14">
+        <v>540134824072</v>
+      </c>
+      <c r="F897" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G897" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="898" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A898" s="12" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B898" s="13">
+        <v>35</v>
+      </c>
+      <c r="D898" s="14">
+        <v>540134824072</v>
+      </c>
+      <c r="F898" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G898" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="899" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A899" s="12" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B899" s="13">
+        <v>38</v>
+      </c>
+      <c r="D899" s="14">
+        <v>503486931661</v>
+      </c>
+      <c r="F899" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G899" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="900" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A900" s="12" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B900" s="13">
+        <v>40</v>
+      </c>
+      <c r="D900" s="14">
+        <v>502434568425</v>
+      </c>
+      <c r="F900" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G900" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="901" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A901" s="12" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B901" s="13">
+        <v>36.369999999999997</v>
+      </c>
+      <c r="D901" s="14">
+        <v>538866028013</v>
+      </c>
+      <c r="F901" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G901" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="902" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A902" s="12" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B902" s="13">
+        <v>55</v>
+      </c>
+      <c r="D902" s="14">
+        <v>501210825163</v>
+      </c>
+      <c r="F902" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G902" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="903" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A903" s="12" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B903" s="13">
+        <v>2655</v>
+      </c>
+      <c r="D903" s="14">
+        <v>501296426060</v>
+      </c>
+      <c r="F903" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G903" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="904" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A904" s="12" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B904" s="13">
+        <v>50</v>
+      </c>
+      <c r="D904" s="14">
+        <v>537676334005</v>
+      </c>
+      <c r="F904" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G904" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="905" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A905" s="12" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B905" s="13">
+        <v>20</v>
+      </c>
+      <c r="D905" s="14">
+        <v>500750438953</v>
+      </c>
+      <c r="F905" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G905" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="906" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A906" s="12" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B906" s="13">
+        <v>65</v>
+      </c>
+      <c r="D906" s="14">
+        <v>436688901359</v>
+      </c>
+      <c r="F906" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G906" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="907" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A907" s="12" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B907" s="13">
+        <v>48</v>
+      </c>
+      <c r="D907" s="14">
+        <v>436286432392</v>
+      </c>
+      <c r="F907" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G907" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="908" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A908" s="12" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B908" s="13">
+        <v>100</v>
+      </c>
+      <c r="D908" s="14">
+        <v>472228088407</v>
+      </c>
+      <c r="F908" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G908" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="909" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A909" s="12" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B909" s="13">
+        <v>24</v>
+      </c>
+      <c r="D909" s="14">
+        <v>435616604031</v>
+      </c>
+      <c r="F909" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G909" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="910" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A910" s="12" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B910" s="13">
+        <v>22</v>
+      </c>
+      <c r="D910" s="14">
+        <v>435116945901</v>
+      </c>
+      <c r="F910" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G910" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="911" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A911" s="12" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B911" s="13">
+        <v>13.33</v>
+      </c>
+      <c r="D911" s="14">
+        <v>434311840688</v>
+      </c>
+      <c r="F911" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G911" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="912" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A912" s="12" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B912" s="13">
+        <v>1890</v>
+      </c>
+      <c r="D912" s="14">
+        <v>434140238243</v>
+      </c>
+      <c r="F912" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G912" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="913" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A913" s="12" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B913" s="13">
+        <v>127</v>
+      </c>
+      <c r="D913" s="14">
+        <v>433390888367</v>
+      </c>
+      <c r="F913" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G913" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="914" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A914" s="12" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B914" s="13">
+        <v>147</v>
+      </c>
+      <c r="D914" s="14">
+        <v>433232586093</v>
+      </c>
+      <c r="F914" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G914" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="915" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A915" s="12" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B915" s="13">
+        <v>3.08</v>
+      </c>
+      <c r="D915" s="14">
+        <v>432910278149</v>
+      </c>
+      <c r="F915" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G915" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="916" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A916" s="12" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B916" s="13">
+        <v>20</v>
+      </c>
+      <c r="D916" s="14">
+        <v>432982289043</v>
+      </c>
+      <c r="F916" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G916" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="917" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A917" s="12" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B917" s="13">
+        <v>170</v>
+      </c>
+      <c r="D917" s="14">
+        <v>432943600714</v>
+      </c>
+      <c r="F917" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G917" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="918" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A918" s="12" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B918" s="13">
+        <v>10</v>
+      </c>
+      <c r="D918" s="14">
+        <v>432041390851</v>
+      </c>
+      <c r="F918" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G918" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="919" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A919" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B919" s="13">
+        <v>8</v>
+      </c>
+      <c r="D919" s="14">
+        <v>468623332583</v>
+      </c>
+      <c r="F919" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G919" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="920" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A920" s="12" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B920" s="13">
+        <v>40</v>
+      </c>
+      <c r="D920" s="14">
+        <v>431999120100</v>
+      </c>
+      <c r="F920" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G920" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="921" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A921" s="12" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B921" s="13">
+        <v>20</v>
+      </c>
+      <c r="D921" s="14">
+        <v>431798587461</v>
+      </c>
+      <c r="F921" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G921" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="922" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A922" s="12" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B922" s="13">
+        <v>1042</v>
+      </c>
+      <c r="D922" s="14">
+        <v>431623179929</v>
+      </c>
+      <c r="F922" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G922" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="923" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A923" s="12" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B923" s="13">
+        <v>116</v>
+      </c>
+      <c r="D923" s="14">
+        <v>431515093095</v>
+      </c>
+      <c r="F923" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G923" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="924" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A924" s="12" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B924" s="13">
+        <v>20</v>
+      </c>
+      <c r="D924" s="14">
+        <v>467900376048</v>
+      </c>
+      <c r="F924" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G924" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="925" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A925" s="12" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B925" s="13">
+        <v>15</v>
+      </c>
+      <c r="D925" s="14">
+        <v>431224708899</v>
+      </c>
+      <c r="F925" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G925" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="926" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A926" s="12" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B926" s="13">
+        <v>350</v>
+      </c>
+      <c r="D926" s="14">
+        <v>431233157396</v>
+      </c>
+      <c r="F926" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G926" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="927" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A927" s="12" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B927" s="13">
+        <v>20</v>
+      </c>
+      <c r="D927" s="14">
+        <v>467733554367</v>
+      </c>
+      <c r="F927" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G927" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="928" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A928" s="12" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B928" s="13">
+        <v>15</v>
+      </c>
+      <c r="D928" s="14">
+        <v>431052196448</v>
+      </c>
+      <c r="F928" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G928" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="929" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A929" s="12" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B929" s="13">
+        <v>20</v>
+      </c>
+      <c r="D929" s="14">
+        <v>431028440494</v>
+      </c>
+      <c r="F929" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G929" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="930" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A930" s="12" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B930" s="13">
+        <v>100</v>
+      </c>
+      <c r="D930" s="14">
+        <v>428002453180</v>
+      </c>
+      <c r="F930" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G930" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="931" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A931" s="12" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B931" s="13">
+        <v>15</v>
+      </c>
+      <c r="D931" s="14">
+        <v>427807995236</v>
+      </c>
+      <c r="F931" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G931" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="932" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A932" s="12" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B932" s="13">
+        <v>9</v>
+      </c>
+      <c r="D932" s="14">
+        <v>427694580608</v>
+      </c>
+      <c r="F932" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G932" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="933" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A933" s="12" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B933" s="13">
+        <v>20</v>
+      </c>
+      <c r="D933" s="14">
+        <v>427533579238</v>
+      </c>
+      <c r="F933" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G933" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="934" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A934" s="12" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B934" s="13">
+        <v>25</v>
+      </c>
+      <c r="D934" s="14">
+        <v>464174174439</v>
+      </c>
+      <c r="F934" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G934" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="935" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A935" s="12" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B935" s="13">
+        <v>38</v>
+      </c>
+      <c r="D935" s="14">
+        <v>427415602527</v>
+      </c>
+      <c r="F935" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G935" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="936" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A936" s="12" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B936" s="13">
+        <v>480.9</v>
+      </c>
+      <c r="D936" s="14">
+        <v>427117826747</v>
+      </c>
+      <c r="F936" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G936" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="937" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A937" s="12" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B937" s="13">
+        <v>10</v>
+      </c>
+      <c r="D937" s="14">
+        <v>427094308323</v>
+      </c>
+      <c r="F937" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G937" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="938" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A938" s="12" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B938" s="13">
+        <v>15</v>
+      </c>
+      <c r="D938" s="14">
+        <v>426952206700</v>
+      </c>
+      <c r="F938" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G938" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="939" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A939" s="12" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B939" s="13">
+        <v>30</v>
+      </c>
+      <c r="D939" s="14">
+        <v>426853295738</v>
+      </c>
+      <c r="F939" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G939" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="940" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A940" s="12" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B940" s="13">
+        <v>45</v>
+      </c>
+      <c r="D940" s="14">
+        <v>426733434338</v>
+      </c>
+      <c r="F940" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G940" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="941" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A941" s="12" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B941" s="13">
+        <v>70</v>
+      </c>
+      <c r="D941" s="14">
+        <v>426695098291</v>
+      </c>
+      <c r="F941" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G941" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="942" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A942" s="12" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B942" s="13">
+        <v>55</v>
+      </c>
+      <c r="D942" s="14">
+        <v>426200720296</v>
+      </c>
+      <c r="F942" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G942" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="943" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A943" s="12" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B943" s="13">
+        <v>22</v>
+      </c>
+      <c r="D943" s="14">
+        <v>426061519046</v>
+      </c>
+      <c r="F943" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G943" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="944" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A944" s="12" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B944" s="13">
+        <v>22</v>
+      </c>
+      <c r="D944" s="14">
+        <v>425912718767</v>
+      </c>
+      <c r="F944" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G944" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="945" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A945" s="12" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B945" s="13">
+        <v>36</v>
+      </c>
+      <c r="D945" s="14">
+        <v>425716680905</v>
+      </c>
+      <c r="F945" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G945" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="946" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A946" s="12" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B946" s="13">
+        <v>65</v>
+      </c>
+      <c r="D946" s="14">
+        <v>425709850517</v>
+      </c>
+      <c r="F946" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G946" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="947" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A947" s="12" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B947" s="13">
+        <v>20</v>
+      </c>
+      <c r="D947" s="14">
+        <v>462160969985</v>
+      </c>
+      <c r="F947" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G947" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="948" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A948" s="12" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B948" s="13">
+        <v>1928</v>
+      </c>
+      <c r="D948" s="14">
+        <v>425516993982</v>
+      </c>
+      <c r="F948" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G948" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="949" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A949" s="12" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B949" s="13">
+        <v>179</v>
+      </c>
+      <c r="D949" s="14">
+        <v>425146062318</v>
+      </c>
+      <c r="F949" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G949" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="950" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A950" s="12" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B950" s="13">
+        <v>1.08</v>
+      </c>
+      <c r="D950" s="14">
+        <v>425107125363</v>
+      </c>
+      <c r="F950" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G950" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="951" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A951" s="12" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B951" s="13">
+        <v>75</v>
+      </c>
+      <c r="D951" s="14">
+        <v>425145939164</v>
+      </c>
+      <c r="F951" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G951" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="952" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A952" s="12" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B952" s="13">
+        <v>18</v>
+      </c>
+      <c r="D952" s="14">
+        <v>424994642618</v>
+      </c>
+      <c r="F952" s="14" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G952" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="953" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A953" s="15" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B953" s="15">
+        <v>540</v>
+      </c>
+      <c r="C953" s="15">
+        <v>20424.88</v>
+      </c>
+      <c r="D953" s="15" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E953" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F953" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G953" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="954" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A954" s="15" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B954" s="15">
+        <v>60</v>
+      </c>
+      <c r="C954" s="15">
+        <v>20546.48</v>
+      </c>
+      <c r="D954" s="15" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E954" s="15" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F954" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G954" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="955" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A955" s="15" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B955" s="15">
+        <v>1000</v>
+      </c>
+      <c r="C955" s="15">
+        <v>20861.259999999998</v>
+      </c>
+      <c r="D955" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E955" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F955" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G955" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="956" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A956" s="15" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B956" s="15">
+        <v>80</v>
+      </c>
+      <c r="C956" s="15">
+        <v>19860.150000000001</v>
+      </c>
+      <c r="D956" s="15" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E956" s="15" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F956" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G956" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="957" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A957" s="15" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B957" s="15">
+        <v>91</v>
+      </c>
+      <c r="C957" s="15">
+        <v>21841.75</v>
+      </c>
+      <c r="D957" s="15" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E957" s="15" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F957" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G957" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="958" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A958" s="15" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B958" s="15">
+        <v>140</v>
+      </c>
+      <c r="C958" s="15">
+        <v>14987.49</v>
+      </c>
+      <c r="D958" s="15" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E958" s="15" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F958" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G958" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="959" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A959" s="15" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B959" s="15">
+        <v>30</v>
+      </c>
+      <c r="C959" s="15">
+        <v>14847.49</v>
+      </c>
+      <c r="D959" s="15" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E959" s="15" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F959" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G959" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="960" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A960" s="15" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B960" s="15">
+        <v>9.57</v>
+      </c>
+      <c r="C960" s="15">
+        <v>14817.49</v>
+      </c>
+      <c r="D960" s="15" t="s">
+        <v>1661</v>
+      </c>
+      <c r="E960" s="15" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F960" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G960" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="961" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A961" s="15" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B961" s="15">
+        <v>30</v>
+      </c>
+      <c r="C961" s="15">
+        <v>14798.35</v>
+      </c>
+      <c r="D961" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E961" s="15" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F961" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G961" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="962" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A962" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B962" s="15">
+        <v>9.57</v>
+      </c>
+      <c r="C962" s="15">
+        <v>14358.35</v>
+      </c>
+      <c r="D962" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E962" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="F962" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G962" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="963" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A963" s="15" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B963" s="15">
+        <v>240</v>
+      </c>
+      <c r="C963" s="15">
+        <v>14120.06</v>
+      </c>
+      <c r="D963" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E963" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F963" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G963" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="964" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A964" s="15" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B964" s="15">
+        <v>15</v>
+      </c>
+      <c r="C964" s="15">
+        <v>15346.06</v>
+      </c>
+      <c r="D964" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E964" s="15" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F964" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G964" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="965" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A965" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B965" s="15">
+        <v>3500</v>
+      </c>
+      <c r="C965" s="15">
+        <v>19667.78</v>
+      </c>
+      <c r="D965" s="15" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E965" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F965" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G965" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="966" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A966" s="15" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B966" s="15">
+        <v>34</v>
+      </c>
+      <c r="C966" s="15">
+        <v>13229.23</v>
+      </c>
+      <c r="D966" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E966" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F966" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G966" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="967" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A967" s="15" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B967" s="15">
+        <v>3500</v>
+      </c>
+      <c r="C967" s="15">
+        <v>14341.09</v>
+      </c>
+      <c r="D967" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E967" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F967" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G967" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="968" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A968" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B968" s="15">
+        <v>20</v>
+      </c>
+      <c r="C968" s="15">
+        <v>13603.59</v>
+      </c>
+      <c r="D968" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E968" s="15" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F968" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G968" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="969" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A969" s="15" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B969" s="15">
+        <v>3500</v>
+      </c>
+      <c r="C969" s="15">
+        <v>18168.939999999999</v>
+      </c>
+      <c r="D969" s="15" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E969" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F969" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G969" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="970" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A970" s="15" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B970" s="15">
+        <v>90</v>
+      </c>
+      <c r="C970" s="15">
+        <v>14928.94</v>
+      </c>
+      <c r="D970" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E970" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F970" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G970" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="971" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A971" s="15" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B971" s="15">
+        <v>7</v>
+      </c>
+      <c r="C971" s="15">
+        <v>14956.03</v>
+      </c>
+      <c r="D971" s="15" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E971" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F971" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G971" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="972" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A972" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B972" s="15">
+        <v>14</v>
+      </c>
+      <c r="C972" s="15">
+        <v>15070.28</v>
+      </c>
+      <c r="D972" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E972" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="F972" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G972" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="973" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A973" s="15" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B973" s="15">
+        <v>1000</v>
+      </c>
+      <c r="C973" s="15">
+        <v>15434.86</v>
+      </c>
+      <c r="D973" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E973" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F973" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G973" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="974" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A974" s="15" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B974" s="15">
+        <v>10</v>
+      </c>
+      <c r="C974" s="15">
+        <v>15138.76</v>
+      </c>
+      <c r="D974" s="15" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E974" s="15" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F974" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G974" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="975" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A975" s="15" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B975" s="15">
+        <v>28</v>
+      </c>
+      <c r="C975" s="15">
+        <v>18615.05</v>
+      </c>
+      <c r="D975" s="15" t="s">
+        <v>1697</v>
+      </c>
+      <c r="E975" s="15" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F975" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G975" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="976" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A976" s="15" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B976" s="15">
+        <v>4000</v>
+      </c>
+      <c r="C976" s="15">
+        <v>19214.8</v>
+      </c>
+      <c r="D976" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E976" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F976" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G976" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="977" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A977" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B977" s="15">
+        <v>3500</v>
+      </c>
+      <c r="C977" s="15">
+        <v>18931.490000000002</v>
+      </c>
+      <c r="D977" s="15" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E977" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F977" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G977" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="978" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A978" s="15" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B978" s="15">
+        <v>3000</v>
+      </c>
+      <c r="C978" s="15">
+        <v>18626.490000000002</v>
+      </c>
+      <c r="D978" s="15" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E978" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F978" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G978" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="979" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A979" s="15" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B979" s="15">
+        <v>172</v>
+      </c>
+      <c r="C979" s="15">
+        <v>13097.39</v>
+      </c>
+      <c r="D979" s="15" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E979" s="15" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F979" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G979" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="980" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A980" s="15" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B980" s="15">
+        <v>1000</v>
+      </c>
+      <c r="C980" s="15">
+        <v>15255.39</v>
+      </c>
+      <c r="D980" s="15" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E980" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F980" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G980" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="981" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A981" s="15" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B981" s="15">
+        <v>1000</v>
+      </c>
+      <c r="C981" s="15">
+        <v>12886.37</v>
+      </c>
+      <c r="D981" s="15" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E981" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F981" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G981" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="982" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A982" s="15" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B982" s="15">
+        <v>5</v>
+      </c>
+      <c r="C982" s="15">
+        <v>13027.37</v>
+      </c>
+      <c r="D982" s="15" t="s">
+        <v>1711</v>
+      </c>
+      <c r="E982" s="15" t="s">
+        <v>1712</v>
+      </c>
+      <c r="F982" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G982" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="983" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A983" s="15" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B983" s="15">
+        <v>48</v>
+      </c>
+      <c r="C983" s="15">
+        <v>13323.04</v>
+      </c>
+      <c r="D983" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E983" s="15" t="s">
+        <v>1715</v>
+      </c>
+      <c r="F983" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G983" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="984" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A984" s="15" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B984" s="15">
+        <v>20</v>
+      </c>
+      <c r="C984" s="15">
+        <v>5503.96</v>
+      </c>
+      <c r="D984" s="15" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E984" s="15" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F984" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G984" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="985" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A985" s="15" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B985" s="15">
+        <v>3500</v>
+      </c>
+      <c r="C985" s="15">
+        <v>5508.96</v>
+      </c>
+      <c r="D985" s="15" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E985" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F985" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G985" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="986" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A986" s="15" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B986" s="15">
+        <v>10</v>
+      </c>
+      <c r="C986" s="15">
+        <v>2158.96</v>
+      </c>
+      <c r="D986" s="15" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E986" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="F986" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G986" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="987" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A987" s="15" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B987" s="15">
+        <v>15</v>
+      </c>
+      <c r="C987" s="15">
+        <v>2564.96</v>
+      </c>
+      <c r="D987" s="15" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E987" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F987" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G987" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="988" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A988" s="15" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B988" s="15">
+        <v>11</v>
+      </c>
+      <c r="C988" s="15">
+        <v>2759.96</v>
+      </c>
+      <c r="D988" s="15" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E988" s="15" t="s">
+        <v>1726</v>
+      </c>
+      <c r="F988" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G988" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="989" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A989" s="15" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B989" s="15">
+        <v>5</v>
+      </c>
+      <c r="C989" s="15">
+        <v>2764.96</v>
+      </c>
+      <c r="D989" s="15" t="s">
+        <v>1728</v>
+      </c>
+      <c r="E989" s="15" t="s">
+        <v>1726</v>
+      </c>
+      <c r="F989" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G989" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="990" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A990" s="15" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B990" s="15">
+        <v>500</v>
+      </c>
+      <c r="C990" s="15">
+        <v>3227.96</v>
+      </c>
+      <c r="D990" s="15" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E990" s="15" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F990" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G990" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="991" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A991" s="15" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B991" s="15">
+        <v>10</v>
+      </c>
+      <c r="C991" s="15">
+        <v>2781.96</v>
+      </c>
+      <c r="D991" s="15" t="s">
+        <v>1732</v>
+      </c>
+      <c r="E991" s="15" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F991" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G991" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="992" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A992" s="15" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B992" s="15">
+        <v>4</v>
+      </c>
+      <c r="C992" s="15">
+        <v>1338.96</v>
+      </c>
+      <c r="D992" s="15" t="s">
+        <v>1734</v>
+      </c>
+      <c r="E992" s="15" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F992" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G992" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="993" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A993" s="15" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B993" s="15">
+        <v>200</v>
+      </c>
+      <c r="C993" s="15">
+        <v>1334.96</v>
+      </c>
+      <c r="D993" s="15" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E993" s="15" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F993" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G993" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="994" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A994" s="15" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B994" s="15">
+        <v>50</v>
+      </c>
+      <c r="C994" s="15">
+        <v>1598.46</v>
+      </c>
+      <c r="D994" s="15" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E994" s="15" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F994" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G994" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="995" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A995" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B995" s="15">
+        <v>20</v>
+      </c>
+      <c r="C995" s="15">
+        <v>1863.46</v>
+      </c>
+      <c r="D995" s="15" t="s">
+        <v>1742</v>
+      </c>
+      <c r="E995" s="15" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F995" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G995" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="996" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A996" s="15" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B996" s="15">
+        <v>150</v>
+      </c>
+      <c r="C996" s="15">
+        <v>2253.46</v>
+      </c>
+      <c r="D996" s="15" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E996" s="15" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F996" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G996" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="997" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A997" s="15" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B997" s="15">
+        <v>104</v>
+      </c>
+      <c r="C997" s="15">
+        <v>2541.46</v>
+      </c>
+      <c r="D997" s="15" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E997" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F997" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G997" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
